--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -39,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,13 +47,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,14 +441,214 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 00:48:38</t>
+          <t>Última actualización: 06:04:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Filas únicas: 0</t>
+          <t>Filas únicas: 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - LP1912 - 07/01/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Última actualización: 00:48:38</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06:03:58</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06:03:58</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>86_EST CHICA-ESC AGRARIA</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>26</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06:03:58</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>56</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06:03:58</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>68</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>06:03:58</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>72</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>06:03:58</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>78</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>LP1912</t>
         </is>
       </c>
     </row>
@@ -454,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,14 +676,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 00:48:38</t>
+          <t>Última actualización: 06:04:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Filas únicas: 0</t>
+          <t>Filas únicas: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - LP1912-215 - 07/01/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Última actualización: 00:48:38</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06:03:58</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>68</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
         </is>
       </c>
     </row>
@@ -489,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,14 +781,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 00:48:38</t>
+          <t>Última actualización: 06:04:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Filas únicas: 0</t>
+          <t>Filas únicas: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - 6203-6173 - 07/01/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Última actualización: 00:48:38</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06:04:08</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>06:09</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>L6173</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:04:08</t>
+          <t>Última actualización: 06:44:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Filas únicas: 7</t>
+          <t>Filas únicas: 13</t>
         </is>
       </c>
     </row>
@@ -460,25 +460,50 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -487,7 +512,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 00:48:38</t>
+          <t>Última actualización: 06:04:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -495,28 +520,38 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>06:03:58</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>06:21</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>18</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>16</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -524,25 +559,30 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>06:03:58</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>06:29</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>86_EST CHICA-ESC AGRARIA</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>26</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>17</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -550,25 +590,30 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>06:03:58</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>06:59</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>14_ABASTO</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>56</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>21</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -576,25 +621,30 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>06:03:58</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>07:11</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>215A_EL PATO</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>68</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>28</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -602,25 +652,30 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>06:03:58</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>07:16</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>11_ETCHEVERRY</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>72</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>32</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -628,25 +683,216 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>06:03:58</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>33</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>07:21</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>26_HERNANDEZ</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>78</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="J12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>39</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>48</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>53</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>53</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>81</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -663,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,7 +922,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:04:08</t>
+          <t>Última actualización: 06:44:19</t>
         </is>
       </c>
     </row>
@@ -695,25 +941,50 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -722,7 +993,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 00:48:38</t>
+          <t>Última actualización: 06:04:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -730,28 +1001,38 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>06:03:58</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>07:11</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>06:44:09</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>215A_EL PATO</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>68</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>28</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -768,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,14 +1062,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:04:08</t>
+          <t>Última actualización: 06:44:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Filas únicas: 2</t>
+          <t>Filas únicas: 3</t>
         </is>
       </c>
     </row>
@@ -800,25 +1081,50 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -827,7 +1133,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 00:48:38</t>
+          <t>Última actualización: 06:04:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -835,28 +1141,69 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>06:04:08</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>06:09</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>06:44:19</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>16</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>06:44:19</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>215A_LA PLATA</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="J7" t="n">
+        <v>58</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:44:19</t>
+          <t>Última actualización: 06:59:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Filas únicas: 13</t>
+          <t>Filas únicas: 16</t>
         </is>
       </c>
     </row>
@@ -485,25 +485,50 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -512,7 +537,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 06:04:08</t>
+          <t>Última actualización: 06:44:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -525,6 +550,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -533,25 +563,30 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>14_ABASTO</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>16</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -564,25 +599,30 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>07:01</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>17</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>13</v>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -595,25 +635,30 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>07:05</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>21</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -626,25 +671,30 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>28</v>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>07:16</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>18</v>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -657,25 +707,30 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>07:16</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>32</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>23</v>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -688,25 +743,30 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>07:17</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>33</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>25</v>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -719,25 +779,30 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>07:21</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>37</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>33</v>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -750,25 +815,30 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>07:23</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>39</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>37</v>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -781,25 +851,30 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>07:32</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>48</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>38</v>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -812,25 +887,30 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>07:37</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>53</v>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>48</v>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -843,25 +923,30 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>07:37</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>27_EL RETIRO</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>53</v>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>70</v>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -874,25 +959,138 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>08:05</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>74</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>75</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>85</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>23_HERNANDEZ</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>81</v>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="O20" t="n">
+        <v>96</v>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -909,7 +1107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,14 +1120,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:44:19</t>
+          <t>Última actualización: 06:59:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Filas únicas: 2</t>
+          <t>Filas únicas: 3</t>
         </is>
       </c>
     </row>
@@ -966,25 +1164,50 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -993,7 +1216,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 06:04:08</t>
+          <t>Última actualización: 06:44:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1006,6 +1229,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1014,25 +1242,66 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>06:44:09</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>215A_EL PATO</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>28</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="n">
+        <v>13</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>06:58:56</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>85</v>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1049,7 +1318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1062,7 +1331,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:44:19</t>
+          <t>Última actualización: 06:59:07</t>
         </is>
       </c>
     </row>
@@ -1106,25 +1375,50 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -1133,7 +1427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 06:04:08</t>
+          <t>Última actualización: 06:44:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1146,6 +1440,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1154,25 +1453,30 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>06:44:19</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>215B_LP-P MOR-1 Y 57</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>16</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>06:59:07</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>44</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
@@ -1185,25 +1489,30 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>06:44:19</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>06:59:07</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>215A_LA PLATA</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>58</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="n">
+        <v>99</v>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:59:07</t>
+          <t>Última actualización: 07:37:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Filas únicas: 16</t>
+          <t>Filas únicas: 18</t>
         </is>
       </c>
     </row>
@@ -510,25 +510,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -537,7 +562,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 06:44:19</t>
+          <t>Última actualización: 06:59:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -555,6 +580,11 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -568,25 +598,30 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>07:04</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>6</v>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -604,25 +639,30 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>07:11</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>13</v>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>18</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -640,25 +680,30 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>17</v>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -676,25 +721,30 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>07:16</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>18</v>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>23</v>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -712,25 +762,30 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>07:21</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>23</v>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>27</v>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -748,25 +803,30 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>07:23</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>25</v>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>34</v>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -784,25 +844,30 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>07:31</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>33</v>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>35</v>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -820,25 +885,30 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>07:35</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>37</v>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>36</v>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -856,25 +926,30 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>07:36</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>27_EL RETIRO</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>38</v>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>44</v>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -892,25 +967,30 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>07:46</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>48</v>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>46</v>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -928,25 +1008,30 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>08:08</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>70</v>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>46</v>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -964,25 +1049,30 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>08:12</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>74</v>
-      </c>
-      <c r="P17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>50</v>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1000,25 +1090,30 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>08:13</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>75</v>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>54</v>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1036,25 +1131,30 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>85</v>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>56</v>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1072,25 +1172,112 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>08:34</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>96</v>
-      </c>
-      <c r="P20" t="inlineStr">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>65</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>67</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>85</v>
+      </c>
+      <c r="U22" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1107,7 +1294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1120,7 +1307,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:59:07</t>
+          <t>Última actualización: 07:37:20</t>
         </is>
       </c>
     </row>
@@ -1189,25 +1376,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -1216,7 +1428,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 06:44:19</t>
+          <t>Última actualización: 06:59:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1234,6 +1446,11 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1247,25 +1464,30 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>07:11</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>13</v>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>46</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1283,25 +1505,30 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>06:58:56</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>07:37:09</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
         <v>85</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1318,7 +1545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1331,14 +1558,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:59:07</t>
+          <t>Última actualización: 07:37:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Filas únicas: 3</t>
+          <t>Filas únicas: 4</t>
         </is>
       </c>
     </row>
@@ -1400,25 +1627,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -1427,7 +1679,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 06:44:19</t>
+          <t>Última actualización: 06:59:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1445,6 +1697,11 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1458,25 +1715,30 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>06:59:07</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>07:43</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>07:37:20</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>215A_LA PLATA</t>
         </is>
       </c>
-      <c r="O6" t="n">
-        <v>44</v>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="n">
+        <v>13</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
@@ -1494,25 +1756,71 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>06:59:07</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>07:37:15</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>40</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>07:37:20</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>215A_LA PLATA</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v>99</v>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="T8" t="n">
+        <v>65</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:37:20</t>
+          <t>Última actualización: 07:58:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Filas únicas: 18</t>
+          <t>Filas únicas: 24</t>
         </is>
       </c>
     </row>
@@ -535,25 +535,50 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -562,7 +587,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 06:59:07</t>
+          <t>Última actualización: 07:37:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -585,6 +610,11 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -603,25 +633,30 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="T6" t="n">
-        <v>10</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -644,25 +679,30 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>07:55</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="T7" t="n">
-        <v>18</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -685,25 +725,30 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>07:59</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>16_SANTA ANA</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>22</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="Y8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -726,25 +771,30 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="T9" t="n">
-        <v>23</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -767,25 +817,30 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>08:04</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="T10" t="n">
-        <v>27</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -808,25 +863,30 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>08:11</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="T11" t="n">
-        <v>34</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -849,25 +909,30 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>08:12</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="T12" t="n">
-        <v>35</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -890,25 +955,30 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>08:13</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="T13" t="n">
-        <v>36</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -931,25 +1001,30 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="T14" t="n">
-        <v>44</v>
-      </c>
-      <c r="U14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -972,25 +1047,30 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>16_P MOR-SANTA ANA</t>
-        </is>
-      </c>
-      <c r="T15" t="n">
-        <v>46</v>
-      </c>
-      <c r="U15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1013,25 +1093,30 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="T16" t="n">
-        <v>46</v>
-      </c>
-      <c r="U16" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1054,25 +1139,30 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>08:27</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
-        </is>
-      </c>
-      <c r="T17" t="n">
-        <v>50</v>
-      </c>
-      <c r="U17" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1095,25 +1185,30 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>08:31</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="T18" t="n">
-        <v>54</v>
-      </c>
-      <c r="U18" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1136,25 +1231,30 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="T19" t="n">
-        <v>56</v>
-      </c>
-      <c r="U19" t="inlineStr">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1177,25 +1277,30 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>81_EL PELIGRO</t>
-        </is>
-      </c>
-      <c r="T20" t="n">
-        <v>65</v>
-      </c>
-      <c r="U20" t="inlineStr">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1218,25 +1323,30 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>08:44</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>14_ABASTO</t>
-        </is>
-      </c>
-      <c r="T21" t="n">
-        <v>67</v>
-      </c>
-      <c r="U21" t="inlineStr">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1259,25 +1369,306 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>09:02</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>215A_EL PATO</t>
         </is>
       </c>
-      <c r="T22" t="n">
-        <v>85</v>
-      </c>
-      <c r="U22" t="inlineStr">
+      <c r="Y23" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>73</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1294,7 +1685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1307,7 +1698,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:37:20</t>
+          <t>Última actualización: 07:58:16</t>
         </is>
       </c>
     </row>
@@ -1401,25 +1792,50 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -1428,7 +1844,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 06:59:07</t>
+          <t>Última actualización: 07:37:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1451,6 +1867,11 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1469,25 +1890,30 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>08:23</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>215B_EL PATO</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>46</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="Y6" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1510,25 +1936,30 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>07:37:09</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>09:02</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>215A_EL PATO</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>85</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="Y7" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1545,7 +1976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1558,7 +1989,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:37:20</t>
+          <t>Última actualización: 07:58:16</t>
         </is>
       </c>
     </row>
@@ -1652,25 +2083,50 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
@@ -1679,7 +2135,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 06:59:07</t>
+          <t>Última actualización: 07:37:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1702,6 +2158,11 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1720,27 +2181,32 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>07:37:20</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>07:50</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>215A_LA PLATA</t>
-        </is>
-      </c>
-      <c r="T6" t="n">
-        <v>13</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>L6173</t>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>07:58:11</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>L6203</t>
         </is>
       </c>
     </row>
@@ -1761,27 +2227,32 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>07:37:15</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>08:17</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>215C_LA PLATA</t>
-        </is>
-      </c>
-      <c r="T7" t="n">
-        <v>40</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>L6203</t>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>07:58:16</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>L6173</t>
         </is>
       </c>
     </row>
@@ -1802,27 +2273,32 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>07:37:20</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>215A_LA PLATA</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
-        <v>65</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>L6173</t>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>07:58:11</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>215D_LA PLATA</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -59,10 +59,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:AE50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,152 +437,367 @@
           <t>LÍNEA 141 - LP1912 - 07/01/2026</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 21</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 22</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 23</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 24</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 25</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Última actualización: 07:58:16</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Última actualización: 08:21:56</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Filas únicas: 24</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Ejecuciones: 49 filas</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>LÍNEA 141 - LP1912 - 07/01/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Unnamed: 1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Unnamed: 2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Unnamed: 3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Unnamed: 4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Unnamed: 5</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Unnamed: 6</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Unnamed: 7</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Unnamed: 8</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Unnamed: 9</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Unnamed: 10</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Unnamed: 11</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Unnamed: 12</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Unnamed: 13</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Unnamed: 14</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Unnamed: 15</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Unnamed: 16</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Unnamed: 17</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Unnamed: 18</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Unnamed: 19</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Unnamed: 20</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -615,6 +830,11 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -661,6 +881,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -707,6 +932,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -753,6 +983,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -799,6 +1034,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -845,6 +1085,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -891,6 +1136,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -937,6 +1187,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -983,6 +1238,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1029,6 +1289,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1075,6 +1340,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1121,6 +1391,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1167,6 +1442,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1213,6 +1493,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1259,6 +1544,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1305,6 +1595,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1351,6 +1646,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1397,6 +1697,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1443,6 +1748,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1489,6 +1799,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1535,6 +1850,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1581,6 +1901,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1627,6 +1952,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -1673,6 +2003,1133 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD35" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AD36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="AD37" t="n">
+        <v>33</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AD38" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD39" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD40" t="n">
+        <v>49</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AD41" t="n">
+        <v>52</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="AD42" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD43" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AD44" t="n">
+        <v>62</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD45" t="n">
+        <v>71</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD46" t="n">
+        <v>71</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD47" t="n">
+        <v>73</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD48" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD49" t="n">
+        <v>82</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD50" t="n">
+        <v>91</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1685,7 +3142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,152 +3151,367 @@
           <t>LÍNEA 141 - LP1912-215 - 07/01/2026</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 21</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 22</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 23</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 24</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 25</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Última actualización: 07:58:16</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Última actualización: 08:21:56</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Filas únicas: 3</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Ejecuciones: 8 filas</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>LÍNEA 141 - LP1912-215 - 07/01/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Unnamed: 1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Unnamed: 2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Unnamed: 3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Unnamed: 4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Unnamed: 5</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Unnamed: 6</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Unnamed: 7</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Unnamed: 8</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Unnamed: 9</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Unnamed: 10</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Unnamed: 11</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Unnamed: 12</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Unnamed: 13</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Unnamed: 14</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Unnamed: 15</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Unnamed: 16</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Unnamed: 17</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Unnamed: 18</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Unnamed: 19</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Unnamed: 20</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1872,6 +3544,11 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1918,6 +3595,11 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1964,6 +3646,113 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1976,7 +3765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1985,152 +3774,367 @@
           <t>LÍNEA 141 - 6203-6173 - 07/01/2026</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 21</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 22</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 23</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 24</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 25</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Última actualización: 07:58:16</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Última actualización: 08:21:56</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Filas únicas: 4</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Ejecuciones: 10 filas</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>LÍNEA 141 - 6203-6173 - 07/01/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Unnamed: 1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Unnamed: 2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Unnamed: 3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Unnamed: 4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Unnamed: 5</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Unnamed: 6</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Unnamed: 7</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Unnamed: 8</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Unnamed: 9</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Unnamed: 10</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Unnamed: 11</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Unnamed: 12</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Unnamed: 13</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Unnamed: 14</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Unnamed: 15</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Unnamed: 16</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Unnamed: 17</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Unnamed: 18</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Unnamed: 19</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Unnamed: 20</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2163,6 +4167,11 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -2209,6 +4218,11 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -2255,6 +4269,11 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -2301,6 +4320,164 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>08:21:51</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>08:21:56</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>08:21:51</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>215D_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>47</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,381 +428,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE50"/>
+  <dimension ref="A1:AE72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>LÍNEA 141 - LP1912 - 07/01/2026</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 4</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 7</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 8</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 9</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 10</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 11</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 12</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 13</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 14</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 15</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 16</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 17</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 18</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 19</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 20</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 21</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 22</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 23</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 24</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 25</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA4" s="1" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB4" s="1" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC4" s="1" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD4" s="1" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE4" s="1" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Última actualización: 08:21:56</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Ejecuciones: 49 filas</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LÍNEA 141 - LP1912 - 07/01/2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Unnamed: 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Unnamed: 2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Unnamed: 3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Unnamed: 4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Unnamed: 5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Unnamed: 6</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Unnamed: 7</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Unnamed: 8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Unnamed: 9</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Unnamed: 10</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Unnamed: 11</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Unnamed: 12</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Unnamed: 13</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Unnamed: 14</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Unnamed: 15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Unnamed: 16</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Unnamed: 17</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Unnamed: 18</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Unnamed: 19</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Unnamed: 20</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Hora_Scrap</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Última actualización: 07:37:20</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Última actualización: 08:27:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -836,8 +625,12 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
+    <row r="3">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Ejecuciones: 71 filas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -858,78 +651,146 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>07:58:05</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>08:01</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="Y6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+    <row r="4">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - LP1912 - 07/01/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>07:58:05</t>
+          <t>Hora_Scrap</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>Hora_Llegada</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="Y7" t="n">
-        <v>6</v>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>LP1912</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr"/>
@@ -938,8 +799,12 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
+    <row r="5">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Última actualización: 07:37:20</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -960,36 +825,18 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>07:58:05</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>08:11</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="Y8" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
     </row>
-    <row r="9">
+    <row r="6">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
@@ -1018,16 +865,16 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1040,7 +887,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
     </row>
-    <row r="10">
+    <row r="7">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
@@ -1069,16 +916,16 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1091,7 +938,7 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
     </row>
-    <row r="11">
+    <row r="8">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
@@ -1120,16 +967,16 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -1142,7 +989,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="9">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
@@ -1171,16 +1018,16 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -1193,7 +1040,7 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
     </row>
-    <row r="13">
+    <row r="10">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
@@ -1222,16 +1069,16 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -1244,7 +1091,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
     </row>
-    <row r="14">
+    <row r="11">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
@@ -1273,16 +1120,16 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -1295,7 +1142,7 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
     </row>
-    <row r="15">
+    <row r="12">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
@@ -1324,16 +1171,16 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
@@ -1346,7 +1193,7 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
     </row>
-    <row r="16">
+    <row r="13">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
@@ -1375,16 +1222,16 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
@@ -1397,7 +1244,7 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
     </row>
-    <row r="17">
+    <row r="14">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
@@ -1426,16 +1273,16 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1448,7 +1295,7 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
     </row>
-    <row r="18">
+    <row r="15">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
@@ -1477,16 +1324,16 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -1499,7 +1346,7 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
     </row>
-    <row r="19">
+    <row r="16">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
@@ -1528,16 +1375,16 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -1550,7 +1397,7 @@
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
     </row>
-    <row r="20">
+    <row r="17">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
@@ -1579,7 +1426,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -1588,7 +1435,7 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -1601,7 +1448,7 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
     </row>
-    <row r="21">
+    <row r="18">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
@@ -1630,16 +1477,16 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -1652,7 +1499,7 @@
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
     </row>
-    <row r="22">
+    <row r="19">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
@@ -1681,16 +1528,16 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -1703,7 +1550,7 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
     </row>
-    <row r="23">
+    <row r="20">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
@@ -1732,16 +1579,16 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -1754,7 +1601,7 @@
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
     </row>
-    <row r="24">
+    <row r="21">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
@@ -1783,16 +1630,16 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -1805,7 +1652,7 @@
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
     </row>
-    <row r="25">
+    <row r="22">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
@@ -1834,16 +1681,16 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -1856,7 +1703,7 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
     </row>
-    <row r="26">
+    <row r="23">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
@@ -1885,16 +1732,16 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -1907,7 +1754,7 @@
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
     </row>
-    <row r="27">
+    <row r="24">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
@@ -1936,16 +1783,16 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -1958,7 +1805,7 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
     </row>
-    <row r="28">
+    <row r="25">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
@@ -1987,16 +1834,16 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -2009,7 +1856,7 @@
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
     </row>
-    <row r="29">
+    <row r="26">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
@@ -2031,36 +1878,36 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="AD29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+    </row>
+    <row r="27">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
@@ -2082,36 +1929,36 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="AD30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+    </row>
+    <row r="28">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
@@ -2133,36 +1980,36 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>08:34</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="AD31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+    </row>
+    <row r="29">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
@@ -2196,16 +2043,16 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -2213,7 +2060,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="30">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
@@ -2247,16 +2094,16 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -2264,7 +2111,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="31">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
@@ -2298,16 +2145,16 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -2315,7 +2162,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="32">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
@@ -2349,7 +2196,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -2358,7 +2205,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -2366,7 +2213,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="33">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
@@ -2400,16 +2247,16 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -2417,7 +2264,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="34">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
@@ -2451,16 +2298,16 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -2468,7 +2315,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="35">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
@@ -2502,16 +2349,16 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -2519,7 +2366,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="36">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
@@ -2553,16 +2400,16 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -2570,7 +2417,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="37">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
@@ -2604,16 +2451,16 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -2621,7 +2468,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="38">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
@@ -2655,16 +2502,16 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -2672,7 +2519,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="39">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
@@ -2706,16 +2553,16 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -2723,7 +2570,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="40">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
@@ -2757,16 +2604,16 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -2774,7 +2621,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="41">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
@@ -2808,16 +2655,16 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -2825,7 +2672,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="42">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
@@ -2859,16 +2706,16 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -2876,7 +2723,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="43">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
@@ -2910,16 +2757,16 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -2927,7 +2774,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="44">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
@@ -2961,16 +2808,16 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -2978,7 +2825,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="45">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
@@ -3012,16 +2859,16 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -3029,7 +2876,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="46">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
@@ -3063,16 +2910,16 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -3080,7 +2927,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="47">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
@@ -3114,18 +2961,1293 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD50" t="n">
+        <v>73</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD51" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD52" t="n">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
           <t>09:52</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>15_ABASTO</t>
         </is>
       </c>
-      <c r="AD50" t="n">
+      <c r="AD53" t="n">
         <v>91</v>
       </c>
-      <c r="AE50" t="inlineStr">
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AD54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AD55" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD56" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD57" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="AD58" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD59" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD60" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AD61" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="AD62" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AD63" t="n">
+        <v>37</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD64" t="n">
+        <v>39</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD65" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="AD66" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD67" t="n">
+        <v>54</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AD68" t="n">
+        <v>57</v>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD69" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD70" t="n">
+        <v>68</v>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD71" t="n">
+        <v>68</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD72" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD73" t="n">
+        <v>77</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD74" t="n">
+        <v>85</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AD75" t="n">
+        <v>97</v>
+      </c>
+      <c r="AE75" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -3142,381 +4264,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>LÍNEA 141 - LP1912-215 - 07/01/2026</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 4</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 7</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 8</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 9</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 10</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 11</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 12</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 13</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 14</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 15</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 16</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 17</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 18</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 19</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 20</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 21</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 22</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 23</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 24</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 25</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA4" s="1" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB4" s="1" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC4" s="1" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD4" s="1" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE4" s="1" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Última actualización: 08:21:56</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Ejecuciones: 8 filas</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LÍNEA 141 - LP1912-215 - 07/01/2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Unnamed: 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Unnamed: 2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Unnamed: 3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Unnamed: 4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Unnamed: 5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Unnamed: 6</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Unnamed: 7</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Unnamed: 8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Unnamed: 9</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Unnamed: 10</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Unnamed: 11</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Unnamed: 12</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Unnamed: 13</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Unnamed: 14</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Unnamed: 15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Unnamed: 16</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Unnamed: 17</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Unnamed: 18</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Unnamed: 19</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Unnamed: 20</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Hora_Scrap</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Última actualización: 07:37:20</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Última actualización: 08:27:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -3550,8 +4461,12 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
+    <row r="3">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Ejecuciones: 9 filas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -3572,78 +4487,146 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>07:58:05</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="Y6" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+    <row r="4">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - LP1912-215 - 07/01/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>07:58:05</t>
+          <t>Hora_Scrap</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>Hora_Llegada</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="Y7" t="n">
-        <v>64</v>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>LP1912</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr"/>
@@ -3652,8 +4635,12 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
+    <row r="5">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Última actualización: 07:37:20</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -3679,31 +4666,13 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+    </row>
+    <row r="6">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
@@ -3725,30 +4694,234 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>08:21:45</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>08:21:45</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>09:41</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>215C_EL PATO</t>
         </is>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD12" t="n">
         <v>80</v>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>08:27:16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -3765,381 +4938,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AE14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>LÍNEA 141 - 6203-6173 - 07/01/2026</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 4</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 7</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 8</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 9</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 10</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 11</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 12</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 13</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 14</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 15</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 16</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 17</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 18</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 19</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 20</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 21</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 22</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 23</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 24</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z4" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 25</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA4" s="1" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB4" s="1" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC4" s="1" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD4" s="1" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE4" s="1" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Última actualización: 08:21:56</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Ejecuciones: 10 filas</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LÍNEA 141 - 6203-6173 - 07/01/2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Unnamed: 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Unnamed: 2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Unnamed: 3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Unnamed: 4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Unnamed: 5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Unnamed: 6</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Unnamed: 7</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Unnamed: 8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Unnamed: 9</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Unnamed: 10</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Unnamed: 11</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Unnamed: 12</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Unnamed: 13</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Unnamed: 14</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Unnamed: 15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Unnamed: 16</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Unnamed: 17</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Unnamed: 18</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Unnamed: 19</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Unnamed: 20</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Hora_Scrap</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Última actualización: 07:37:20</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Última actualización: 08:27:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -4173,8 +5135,12 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
+    <row r="3">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Ejecuciones: 13 filas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -4195,78 +5161,146 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>07:58:11</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>08:19</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>215C_LA PLATA</t>
-        </is>
-      </c>
-      <c r="Y6" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>L6203</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+    <row r="4">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - 6203-6173 - 07/01/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>07:58:16</t>
+          <t>Hora_Scrap</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>Hora_Llegada</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
-        </is>
-      </c>
-      <c r="Y7" t="n">
-        <v>48</v>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr"/>
@@ -4275,8 +5309,12 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
+    <row r="5">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Última actualización: 07:37:20</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -4297,36 +5335,18 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>07:58:11</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>215D_LA PLATA</t>
-        </is>
-      </c>
-      <c r="Y8" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>L6203</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
     </row>
-    <row r="9">
+    <row r="6">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
@@ -4348,36 +5368,36 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>08:21:51</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>08:26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>07:58:11</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>215C_LA PLATA</t>
         </is>
       </c>
-      <c r="AD9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE9" t="inlineStr">
+      <c r="Y9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>
       </c>
-    </row>
-    <row r="10">
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+    </row>
+    <row r="7">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
@@ -4399,36 +5419,36 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>08:21:56</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>07:58:16</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>215A_LA PLATA</t>
         </is>
       </c>
-      <c r="AD10" t="n">
-        <v>31</v>
-      </c>
-      <c r="AE10" t="inlineStr">
+      <c r="Y10" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
       </c>
-    </row>
-    <row r="11">
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+    </row>
+    <row r="8">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
@@ -4450,32 +5470,338 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>07:58:11</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>215D_LA PLATA</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>08:21:51</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>08:21:56</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD13" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>08:21:51</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>09:08</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>215D_LA PLATA</t>
         </is>
       </c>
-      <c r="AD11" t="n">
+      <c r="AD14" t="n">
         <v>47</v>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>08:27:27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>08:27:22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>215D_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>08:27:27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="AD17" t="n">
+        <v>96</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>L6173</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE72"/>
+  <dimension ref="A1:AE95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Última actualización: 08:27:27</t>
+          <t>Última actualización: 08:29:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -628,7 +628,7 @@
     <row r="3">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Ejecuciones: 71 filas</t>
+          <t>Ejecuciones: 94 filas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -4253,6 +4253,1179 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AD76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD77" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD78" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="AD79" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD80" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD81" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AD82" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="AD83" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD84" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AD85" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD86" t="n">
+        <v>35</v>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD87" t="n">
+        <v>41</v>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="AD88" t="n">
+        <v>47</v>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD89" t="n">
+        <v>52</v>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AD90" t="n">
+        <v>54</v>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD91" t="n">
+        <v>63</v>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr"/>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AD92" t="n">
+        <v>64</v>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD93" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD94" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD95" t="n">
+        <v>73</v>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr"/>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD96" t="n">
+        <v>74</v>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr"/>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD97" t="n">
+        <v>83</v>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr"/>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AD98" t="n">
+        <v>94</v>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4264,7 +5437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AE12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4427,7 +5600,7 @@
     <row r="2">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Última actualización: 08:27:27</t>
+          <t>Última actualización: 08:29:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -4464,7 +5637,7 @@
     <row r="3">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Ejecuciones: 9 filas</t>
+          <t>Ejecuciones: 11 filas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -4927,6 +6100,108 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD15" t="n">
+        <v>73</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4938,7 +6213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE14"/>
+  <dimension ref="A1:AE17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5101,7 +6376,7 @@
     <row r="2">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Última actualización: 08:27:27</t>
+          <t>Última actualización: 08:29:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -5138,7 +6413,7 @@
     <row r="3">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Ejecuciones: 13 filas</t>
+          <t>Ejecuciones: 16 filas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -5805,6 +7080,159 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>08:29:46</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>08:29:40</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>215D_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD19" t="n">
+        <v>39</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>08:29:46</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="AD20" t="n">
+        <v>93</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -59,10 +59,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,168 +428,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE95"/>
+  <dimension ref="A1:AE121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Fecha: 07/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Total: 117 horarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>LÍNEA 141 - LP1912 - 07/01/2026</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 1</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 2</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 3</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 4</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 5</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 6</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 7</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 8</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 9</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 10</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 11</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 12</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 13</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 14</t>
         </is>
       </c>
-      <c r="P4" s="1" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 15</t>
         </is>
       </c>
-      <c r="Q4" s="1" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 16</t>
         </is>
       </c>
-      <c r="R4" s="1" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 17</t>
         </is>
       </c>
-      <c r="S4" s="1" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 18</t>
         </is>
       </c>
-      <c r="T4" s="1" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 19</t>
         </is>
       </c>
-      <c r="U4" s="1" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 20</t>
         </is>
       </c>
-      <c r="V4" s="1" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 21</t>
         </is>
       </c>
-      <c r="W4" s="1" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 22</t>
         </is>
       </c>
-      <c r="X4" s="1" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 23</t>
         </is>
       </c>
-      <c r="Y4" s="1" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 24</t>
         </is>
       </c>
-      <c r="Z4" s="1" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 25</t>
         </is>
       </c>
-      <c r="AA4" s="1" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="AB4" s="1" t="inlineStr">
+      <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="AC4" s="1" t="inlineStr">
+      <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="AD4" s="1" t="inlineStr">
+      <c r="AD4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="AE4" s="1" t="inlineStr">
+      <c r="AE4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Última actualización: 08:29:46</t>
         </is>
@@ -625,8 +646,8 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ejecuciones: 94 filas</t>
         </is>
@@ -662,7 +683,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
     </row>
-    <row r="4">
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>LÍNEA 141 - LP1912 - 07/01/2026</t>
@@ -799,7 +820,7 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
     </row>
-    <row r="5">
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>Última actualización: 07:37:20</t>
@@ -836,7 +857,7 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
@@ -887,7 +908,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
     </row>
-    <row r="7">
+    <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
@@ -938,7 +959,7 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
@@ -989,7 +1010,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
     </row>
-    <row r="9">
+    <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
@@ -1040,7 +1061,7 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
     </row>
-    <row r="10">
+    <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
@@ -1091,7 +1112,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
     </row>
-    <row r="11">
+    <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
@@ -1142,7 +1163,7 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
@@ -1193,7 +1214,7 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
     </row>
-    <row r="13">
+    <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
@@ -1244,7 +1265,7 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
     </row>
-    <row r="14">
+    <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
@@ -1295,7 +1316,7 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
     </row>
-    <row r="15">
+    <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
@@ -1346,7 +1367,7 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
     </row>
-    <row r="16">
+    <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
@@ -1397,7 +1418,7 @@
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
     </row>
-    <row r="17">
+    <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
@@ -1448,7 +1469,7 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
     </row>
-    <row r="18">
+    <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
@@ -1499,7 +1520,7 @@
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
     </row>
-    <row r="19">
+    <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
@@ -1550,7 +1571,7 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
     </row>
-    <row r="20">
+    <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
@@ -1601,7 +1622,7 @@
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
     </row>
-    <row r="21">
+    <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
@@ -1652,7 +1673,7 @@
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
     </row>
-    <row r="22">
+    <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
@@ -1703,7 +1724,7 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
     </row>
-    <row r="23">
+    <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
@@ -1754,7 +1775,7 @@
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
     </row>
-    <row r="24">
+    <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
@@ -1805,7 +1826,7 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
     </row>
-    <row r="25">
+    <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
@@ -1856,7 +1877,7 @@
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
     </row>
-    <row r="26">
+    <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
@@ -1907,7 +1928,7 @@
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
     </row>
-    <row r="27">
+    <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
@@ -1958,7 +1979,7 @@
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
     </row>
-    <row r="28">
+    <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
@@ -2009,7 +2030,7 @@
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
     </row>
-    <row r="29">
+    <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
@@ -2060,7 +2081,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
@@ -2111,7 +2132,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
@@ -2162,7 +2183,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
@@ -2213,7 +2234,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
@@ -2264,7 +2285,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
@@ -2315,7 +2336,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
@@ -2366,7 +2387,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
@@ -2417,7 +2438,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
@@ -2468,7 +2489,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
@@ -2519,7 +2540,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
@@ -2570,7 +2591,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
@@ -2621,7 +2642,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
@@ -2672,7 +2693,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
@@ -2723,7 +2744,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
@@ -2774,7 +2795,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
@@ -2825,7 +2846,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
@@ -2876,7 +2897,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
@@ -2927,7 +2948,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
@@ -2978,7 +2999,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
@@ -3029,7 +3050,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
@@ -3080,7 +3101,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
@@ -3131,7 +3152,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
@@ -3182,7 +3203,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
@@ -3233,7 +3254,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
@@ -3284,7 +3305,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
@@ -3335,7 +3356,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
@@ -3386,7 +3407,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
@@ -3437,7 +3458,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
@@ -3488,7 +3509,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
@@ -3539,7 +3560,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
@@ -3590,7 +3611,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
@@ -3641,7 +3662,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
@@ -3692,7 +3713,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
@@ -3743,7 +3764,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
@@ -3794,7 +3815,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
@@ -3845,7 +3866,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
@@ -3896,7 +3917,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
@@ -3947,7 +3968,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
@@ -3998,7 +4019,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
@@ -4049,7 +4070,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
@@ -4100,7 +4121,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
@@ -4151,7 +4172,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
@@ -4202,7 +4223,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
@@ -4253,7 +4274,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
@@ -4304,7 +4325,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
@@ -4355,7 +4376,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
@@ -4406,7 +4427,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
@@ -4457,7 +4478,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
@@ -4508,7 +4529,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
@@ -4559,7 +4580,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
@@ -4610,7 +4631,7 @@
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
@@ -4661,7 +4682,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
@@ -4712,7 +4733,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
@@ -4763,7 +4784,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
@@ -4814,7 +4835,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
@@ -4865,7 +4886,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
@@ -4916,7 +4937,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
@@ -4967,7 +4988,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
@@ -5018,7 +5039,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
@@ -5069,7 +5090,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
@@ -5120,7 +5141,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
@@ -5171,7 +5192,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
@@ -5222,7 +5243,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
@@ -5273,7 +5294,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
@@ -5324,7 +5345,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
@@ -5375,7 +5396,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
@@ -5426,6 +5447,1179 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AD99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD100" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD101" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="inlineStr"/>
+      <c r="Y102" t="inlineStr"/>
+      <c r="Z102" t="inlineStr"/>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="AD102" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="inlineStr"/>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD103" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
+      <c r="X104" t="inlineStr"/>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr"/>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD104" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr"/>
+      <c r="X105" t="inlineStr"/>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr"/>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AD105" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr"/>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="AD106" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="inlineStr"/>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD107" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="inlineStr"/>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr"/>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AD108" t="n">
+        <v>33</v>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr"/>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD109" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+      <c r="X110" t="inlineStr"/>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr"/>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD110" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="inlineStr"/>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="AD111" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD112" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+      <c r="X113" t="inlineStr"/>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr"/>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AD113" t="n">
+        <v>53</v>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+      <c r="X114" t="inlineStr"/>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr"/>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD114" t="n">
+        <v>61</v>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AD115" t="n">
+        <v>62</v>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AD116" t="n">
+        <v>64</v>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AD117" t="n">
+        <v>64</v>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="inlineStr"/>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr"/>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD118" t="n">
+        <v>71</v>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+      <c r="X119" t="inlineStr"/>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr"/>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD119" t="n">
+        <v>73</v>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr"/>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD120" t="n">
+        <v>81</v>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr"/>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AD121" t="n">
+        <v>93</v>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5437,168 +6631,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE12"/>
+  <dimension ref="A1:AE17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - LP1912-215</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Fecha: 07/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Total: 13 horarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>LÍNEA 141 - LP1912-215 - 07/01/2026</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 1</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 2</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 3</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 4</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 5</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 6</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 7</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 8</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 9</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 10</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 11</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 12</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 13</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 14</t>
         </is>
       </c>
-      <c r="P4" s="1" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 15</t>
         </is>
       </c>
-      <c r="Q4" s="1" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 16</t>
         </is>
       </c>
-      <c r="R4" s="1" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 17</t>
         </is>
       </c>
-      <c r="S4" s="1" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 18</t>
         </is>
       </c>
-      <c r="T4" s="1" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 19</t>
         </is>
       </c>
-      <c r="U4" s="1" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 20</t>
         </is>
       </c>
-      <c r="V4" s="1" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 21</t>
         </is>
       </c>
-      <c r="W4" s="1" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 22</t>
         </is>
       </c>
-      <c r="X4" s="1" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 23</t>
         </is>
       </c>
-      <c r="Y4" s="1" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 24</t>
         </is>
       </c>
-      <c r="Z4" s="1" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 25</t>
         </is>
       </c>
-      <c r="AA4" s="1" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="AB4" s="1" t="inlineStr">
+      <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="AC4" s="1" t="inlineStr">
+      <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="AD4" s="1" t="inlineStr">
+      <c r="AD4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="AE4" s="1" t="inlineStr">
+      <c r="AE4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Última actualización: 08:29:46</t>
         </is>
@@ -5634,8 +6849,8 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ejecuciones: 11 filas</t>
         </is>
@@ -5671,7 +6886,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
     </row>
-    <row r="4">
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>LÍNEA 141 - LP1912-215 - 07/01/2026</t>
@@ -5808,7 +7023,7 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
     </row>
-    <row r="5">
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>Última actualización: 07:37:20</t>
@@ -5845,7 +7060,7 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
@@ -5896,7 +7111,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
     </row>
-    <row r="7">
+    <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
@@ -5947,7 +7162,7 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
@@ -5998,7 +7213,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
@@ -6049,7 +7264,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
@@ -6100,7 +7315,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
@@ -6151,7 +7366,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
@@ -6202,6 +7417,108 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD16" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD17" t="n">
+        <v>71</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6213,168 +7530,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE17"/>
+  <dimension ref="A1:AE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - 6203-6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Fecha: 07/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Total: 19 horarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>LÍNEA 141 - 6203-6173 - 07/01/2026</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 1</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 2</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 3</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 4</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 5</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 6</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 7</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 8</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 9</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 10</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 11</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 12</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 13</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 14</t>
         </is>
       </c>
-      <c r="P4" s="1" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 15</t>
         </is>
       </c>
-      <c r="Q4" s="1" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 16</t>
         </is>
       </c>
-      <c r="R4" s="1" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 17</t>
         </is>
       </c>
-      <c r="S4" s="1" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 18</t>
         </is>
       </c>
-      <c r="T4" s="1" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 19</t>
         </is>
       </c>
-      <c r="U4" s="1" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 20</t>
         </is>
       </c>
-      <c r="V4" s="1" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 21</t>
         </is>
       </c>
-      <c r="W4" s="1" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 22</t>
         </is>
       </c>
-      <c r="X4" s="1" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 23</t>
         </is>
       </c>
-      <c r="Y4" s="1" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 24</t>
         </is>
       </c>
-      <c r="Z4" s="1" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Unnamed: 25</t>
         </is>
       </c>
-      <c r="AA4" s="1" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="AB4" s="1" t="inlineStr">
+      <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="AC4" s="1" t="inlineStr">
+      <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="AD4" s="1" t="inlineStr">
+      <c r="AD4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="AE4" s="1" t="inlineStr">
+      <c r="AE4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Última actualización: 08:29:46</t>
         </is>
@@ -6410,8 +7748,8 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ejecuciones: 16 filas</t>
         </is>
@@ -6447,7 +7785,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
     </row>
-    <row r="4">
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>LÍNEA 141 - 6203-6173 - 07/01/2026</t>
@@ -6584,7 +7922,7 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
     </row>
-    <row r="5">
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>Última actualización: 07:37:20</t>
@@ -6621,7 +7959,7 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
@@ -6672,7 +8010,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
     </row>
-    <row r="7">
+    <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
@@ -6723,7 +8061,7 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
@@ -6774,7 +8112,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
     </row>
-    <row r="9">
+    <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
@@ -6825,7 +8163,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
@@ -6876,7 +8214,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
@@ -6927,7 +8265,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
@@ -6978,7 +8316,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
@@ -7029,7 +8367,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
@@ -7080,7 +8418,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
@@ -7131,7 +8469,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
@@ -7182,7 +8520,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
@@ -7233,6 +8571,159 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>08:31:11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>08:31:06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>215D_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>08:31:11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>92</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE121"/>
+  <dimension ref="A1:AJ147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,14 +448,14 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total: 117 horarios</t>
+          <t>Total: 143 horarios</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LÍNEA 141 - LP1912 - 07/01/2026</t>
+          <t>LÍNEA 141 - LP1912</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -585,34 +585,59 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 26</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 27</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 28</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 29</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 30</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>Parada</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 08:29:46</t>
+          <t>Fecha: 07/01/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -645,11 +670,16 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ejecuciones: 94 filas</t>
+          <t>Total: 117 horarios</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -682,6 +712,11 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -791,39 +826,64 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Unnamed: 21</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Unnamed: 22</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Unnamed: 23</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Unnamed: 24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Unnamed: 25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Última actualización: 07:37:20</t>
+          <t>Última actualización: 08:29:46</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -856,9 +916,18 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ejecuciones: 94 filas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -879,78 +948,151 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>07:58:05</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>08:01</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="Y9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - LP1912 - 07/01/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>07:58:05</t>
+          <t>Hora_Scrap</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>Hora_Llegada</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="Y10" t="n">
-        <v>6</v>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>LP1912</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr"/>
@@ -958,9 +1100,18 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Última actualización: 07:37:20</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -981,34 +1132,21 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>07:58:05</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>08:11</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="Y11" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1039,16 +1177,16 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -1060,6 +1198,11 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1090,16 +1233,16 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -1111,6 +1254,11 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1141,16 +1289,16 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -1162,6 +1310,11 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1192,16 +1345,16 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
@@ -1213,6 +1366,11 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1243,16 +1401,16 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
@@ -1264,6 +1422,11 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1294,16 +1457,16 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1315,6 +1478,11 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1345,16 +1513,16 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -1366,6 +1534,11 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1396,16 +1569,16 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -1417,6 +1590,11 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1447,16 +1625,16 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -1468,6 +1646,11 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1498,16 +1681,16 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -1519,6 +1702,11 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1549,16 +1737,16 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -1570,6 +1758,11 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1600,7 +1793,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -1609,7 +1802,7 @@
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -1621,6 +1814,11 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1651,16 +1849,16 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -1672,6 +1870,11 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1702,16 +1905,16 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -1723,6 +1926,11 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1753,16 +1961,16 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -1774,6 +1982,11 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1804,16 +2017,16 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -1825,6 +2038,11 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -1855,16 +2073,16 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -1876,6 +2094,11 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -1906,16 +2129,16 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -1927,6 +2150,11 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -1957,16 +2185,16 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -1978,6 +2206,11 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -2008,16 +2241,16 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -2029,6 +2262,11 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -2052,34 +2290,39 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="AD32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>73</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -2103,34 +2346,39 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="AD33" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -2154,34 +2402,39 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>08:34</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="AD34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -2217,22 +2470,27 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -2268,22 +2526,27 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -2319,22 +2582,27 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -2370,7 +2638,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -2379,13 +2647,18 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -2421,22 +2694,27 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -2472,22 +2750,27 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -2523,22 +2806,27 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -2574,22 +2862,27 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -2625,22 +2918,27 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -2676,22 +2974,27 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -2727,22 +3030,27 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -2778,22 +3086,27 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -2829,22 +3142,27 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -2880,22 +3198,27 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -2931,22 +3254,27 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -2982,22 +3310,27 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -3033,22 +3366,27 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -3084,22 +3422,27 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -3135,22 +3478,27 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -3181,27 +3529,32 @@
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>08:27:16</t>
+          <t>08:21:45</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -3232,27 +3585,32 @@
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>08:27:16</t>
+          <t>08:21:45</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -3283,27 +3641,32 @@
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>08:27:16</t>
+          <t>08:21:45</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -3339,22 +3702,27 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -3390,22 +3758,27 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -3441,22 +3814,27 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -3492,7 +3870,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -3501,13 +3879,18 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -3543,22 +3926,27 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -3594,22 +3982,27 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -3645,22 +4038,27 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -3696,22 +4094,27 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -3747,22 +4150,27 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -3798,22 +4206,27 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -3849,22 +4262,27 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -3900,22 +4318,27 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -3951,22 +4374,27 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -4002,22 +4430,27 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -4053,22 +4486,27 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -4104,22 +4542,27 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -4155,22 +4598,27 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -4206,22 +4654,27 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -4257,22 +4710,27 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -4303,27 +4761,32 @@
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>08:29:35</t>
+          <t>08:27:16</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -4354,27 +4817,32 @@
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>08:29:35</t>
+          <t>08:27:16</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -4405,27 +4873,32 @@
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>08:29:35</t>
+          <t>08:27:16</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -4461,22 +4934,27 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -4512,22 +4990,27 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
@@ -4563,7 +5046,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -4572,13 +5055,18 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
@@ -4614,22 +5102,27 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
@@ -4665,22 +5158,27 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
@@ -4716,22 +5214,27 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
@@ -4767,22 +5270,27 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
@@ -4818,22 +5326,27 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
@@ -4869,22 +5382,27 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
@@ -4920,22 +5438,27 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
@@ -4971,22 +5494,27 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
@@ -5022,22 +5550,27 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
@@ -5073,22 +5606,27 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
@@ -5124,22 +5662,27 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="AE92" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
@@ -5175,22 +5718,27 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr"/>
+      <c r="AJ93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
@@ -5226,22 +5774,27 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AE94" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr"/>
+      <c r="AJ94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
@@ -5277,22 +5830,27 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
@@ -5328,22 +5886,27 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
@@ -5379,22 +5942,27 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr"/>
+      <c r="AJ97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
@@ -5430,22 +5998,27 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr"/>
+      <c r="AJ98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
@@ -5476,27 +6049,32 @@
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>08:31:01</t>
+          <t>08:29:35</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="AE99" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
@@ -5527,27 +6105,32 @@
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>08:31:01</t>
+          <t>08:29:35</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="AE100" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr"/>
+      <c r="AJ100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
@@ -5578,27 +6161,32 @@
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>08:31:01</t>
+          <t>08:29:35</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="AE101" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr"/>
+      <c r="AJ101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
@@ -5634,22 +6222,27 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
@@ -5685,22 +6278,27 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
@@ -5736,7 +6334,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -5745,13 +6343,18 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE104" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
@@ -5787,22 +6390,27 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AE105" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
@@ -5838,22 +6446,27 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AE106" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
@@ -5889,22 +6502,27 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr"/>
+      <c r="AJ107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
@@ -5940,22 +6558,27 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="AE108" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr"/>
+      <c r="AJ108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
@@ -5991,22 +6614,27 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AE109" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr"/>
+      <c r="AJ109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
@@ -6042,22 +6670,27 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr"/>
+      <c r="AJ110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
@@ -6093,22 +6726,27 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="AE111" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr"/>
+      <c r="AJ111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
@@ -6144,22 +6782,27 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr"/>
+      <c r="AJ112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
@@ -6195,22 +6838,27 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr"/>
+      <c r="AJ113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
@@ -6246,22 +6894,27 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="AE114" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr"/>
+      <c r="AJ114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
@@ -6297,22 +6950,27 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="AE115" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr"/>
+      <c r="AJ115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
@@ -6348,22 +7006,27 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr"/>
+      <c r="AJ116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
@@ -6399,22 +7062,27 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr"/>
+      <c r="AH117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr"/>
+      <c r="AJ117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
@@ -6450,22 +7118,27 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="AE118" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr"/>
+      <c r="AJ118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
@@ -6501,22 +7174,27 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="AE119" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
@@ -6552,22 +7230,27 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="AE120" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="inlineStr"/>
+      <c r="AH120" t="inlineStr"/>
+      <c r="AI120" t="inlineStr"/>
+      <c r="AJ120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
@@ -6603,20 +7286,1481 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD121" t="n">
+        <v>71</v>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="inlineStr"/>
+      <c r="AH121" t="inlineStr"/>
+      <c r="AI121" t="inlineStr"/>
+      <c r="AJ121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr"/>
+      <c r="Z122" t="inlineStr"/>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD122" t="n">
+        <v>73</v>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="inlineStr"/>
+      <c r="AH122" t="inlineStr"/>
+      <c r="AI122" t="inlineStr"/>
+      <c r="AJ122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+      <c r="X123" t="inlineStr"/>
+      <c r="Y123" t="inlineStr"/>
+      <c r="Z123" t="inlineStr"/>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD123" t="n">
+        <v>81</v>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="inlineStr"/>
+      <c r="AH123" t="inlineStr"/>
+      <c r="AI123" t="inlineStr"/>
+      <c r="AJ123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+      <c r="W124" t="inlineStr"/>
+      <c r="X124" t="inlineStr"/>
+      <c r="Y124" t="inlineStr"/>
+      <c r="Z124" t="inlineStr"/>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
+      <c r="AC124" t="inlineStr">
         <is>
           <t>11_ETCHEVERRY</t>
         </is>
       </c>
-      <c r="AD121" t="n">
+      <c r="AD124" t="n">
         <v>93</v>
       </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>LP1912</t>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="inlineStr"/>
+      <c r="AH124" t="inlineStr"/>
+      <c r="AI124" t="inlineStr"/>
+      <c r="AJ124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
+      <c r="X125" t="inlineStr"/>
+      <c r="Y125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr"/>
+      <c r="AA125" t="inlineStr"/>
+      <c r="AB125" t="inlineStr"/>
+      <c r="AC125" t="inlineStr"/>
+      <c r="AD125" t="inlineStr"/>
+      <c r="AE125" t="inlineStr"/>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AH125" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
+      <c r="W126" t="inlineStr"/>
+      <c r="X126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr"/>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
+      <c r="AC126" t="inlineStr"/>
+      <c r="AD126" t="inlineStr"/>
+      <c r="AE126" t="inlineStr"/>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="AH126" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
+      <c r="W127" t="inlineStr"/>
+      <c r="X127" t="inlineStr"/>
+      <c r="Y127" t="inlineStr"/>
+      <c r="Z127" t="inlineStr"/>
+      <c r="AA127" t="inlineStr"/>
+      <c r="AB127" t="inlineStr"/>
+      <c r="AC127" t="inlineStr"/>
+      <c r="AD127" t="inlineStr"/>
+      <c r="AE127" t="inlineStr"/>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AH127" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
+      <c r="W128" t="inlineStr"/>
+      <c r="X128" t="inlineStr"/>
+      <c r="Y128" t="inlineStr"/>
+      <c r="Z128" t="inlineStr"/>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="inlineStr"/>
+      <c r="AC128" t="inlineStr"/>
+      <c r="AD128" t="inlineStr"/>
+      <c r="AE128" t="inlineStr"/>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AH128" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+      <c r="W129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="inlineStr"/>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
+      <c r="AC129" t="inlineStr"/>
+      <c r="AD129" t="inlineStr"/>
+      <c r="AE129" t="inlineStr"/>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AH129" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="inlineStr"/>
+      <c r="Y130" t="inlineStr"/>
+      <c r="Z130" t="inlineStr"/>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr"/>
+      <c r="AC130" t="inlineStr"/>
+      <c r="AD130" t="inlineStr"/>
+      <c r="AE130" t="inlineStr"/>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="AH130" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
+      <c r="W131" t="inlineStr"/>
+      <c r="X131" t="inlineStr"/>
+      <c r="Y131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr"/>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr"/>
+      <c r="AC131" t="inlineStr"/>
+      <c r="AD131" t="inlineStr"/>
+      <c r="AE131" t="inlineStr"/>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="AH131" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
+      <c r="W132" t="inlineStr"/>
+      <c r="X132" t="inlineStr"/>
+      <c r="Y132" t="inlineStr"/>
+      <c r="Z132" t="inlineStr"/>
+      <c r="AA132" t="inlineStr"/>
+      <c r="AB132" t="inlineStr"/>
+      <c r="AC132" t="inlineStr"/>
+      <c r="AD132" t="inlineStr"/>
+      <c r="AE132" t="inlineStr"/>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AH132" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
+      <c r="W133" t="inlineStr"/>
+      <c r="X133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr"/>
+      <c r="Z133" t="inlineStr"/>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
+      <c r="AC133" t="inlineStr"/>
+      <c r="AD133" t="inlineStr"/>
+      <c r="AE133" t="inlineStr"/>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AH133" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr"/>
+      <c r="W134" t="inlineStr"/>
+      <c r="X134" t="inlineStr"/>
+      <c r="Y134" t="inlineStr"/>
+      <c r="Z134" t="inlineStr"/>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
+      <c r="AC134" t="inlineStr"/>
+      <c r="AD134" t="inlineStr"/>
+      <c r="AE134" t="inlineStr"/>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AH134" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
+      <c r="W135" t="inlineStr"/>
+      <c r="X135" t="inlineStr"/>
+      <c r="Y135" t="inlineStr"/>
+      <c r="Z135" t="inlineStr"/>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="inlineStr"/>
+      <c r="AD135" t="inlineStr"/>
+      <c r="AE135" t="inlineStr"/>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="AH135" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
+      <c r="W136" t="inlineStr"/>
+      <c r="X136" t="inlineStr"/>
+      <c r="Y136" t="inlineStr"/>
+      <c r="Z136" t="inlineStr"/>
+      <c r="AA136" t="inlineStr"/>
+      <c r="AB136" t="inlineStr"/>
+      <c r="AC136" t="inlineStr"/>
+      <c r="AD136" t="inlineStr"/>
+      <c r="AE136" t="inlineStr"/>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AH136" t="n">
+        <v>47</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
+      <c r="W137" t="inlineStr"/>
+      <c r="X137" t="inlineStr"/>
+      <c r="Y137" t="inlineStr"/>
+      <c r="Z137" t="inlineStr"/>
+      <c r="AA137" t="inlineStr"/>
+      <c r="AB137" t="inlineStr"/>
+      <c r="AC137" t="inlineStr"/>
+      <c r="AD137" t="inlineStr"/>
+      <c r="AE137" t="inlineStr"/>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AH137" t="n">
+        <v>49</v>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr"/>
+      <c r="W138" t="inlineStr"/>
+      <c r="X138" t="inlineStr"/>
+      <c r="Y138" t="inlineStr"/>
+      <c r="Z138" t="inlineStr"/>
+      <c r="AA138" t="inlineStr"/>
+      <c r="AB138" t="inlineStr"/>
+      <c r="AC138" t="inlineStr"/>
+      <c r="AD138" t="inlineStr"/>
+      <c r="AE138" t="inlineStr"/>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AH138" t="n">
+        <v>51</v>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr"/>
+      <c r="W139" t="inlineStr"/>
+      <c r="X139" t="inlineStr"/>
+      <c r="Y139" t="inlineStr"/>
+      <c r="Z139" t="inlineStr"/>
+      <c r="AA139" t="inlineStr"/>
+      <c r="AB139" t="inlineStr"/>
+      <c r="AC139" t="inlineStr"/>
+      <c r="AD139" t="inlineStr"/>
+      <c r="AE139" t="inlineStr"/>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AH139" t="n">
+        <v>58</v>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr"/>
+      <c r="W140" t="inlineStr"/>
+      <c r="X140" t="inlineStr"/>
+      <c r="Y140" t="inlineStr"/>
+      <c r="Z140" t="inlineStr"/>
+      <c r="AA140" t="inlineStr"/>
+      <c r="AB140" t="inlineStr"/>
+      <c r="AC140" t="inlineStr"/>
+      <c r="AD140" t="inlineStr"/>
+      <c r="AE140" t="inlineStr"/>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AH140" t="n">
+        <v>59</v>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr"/>
+      <c r="Y141" t="inlineStr"/>
+      <c r="Z141" t="inlineStr"/>
+      <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="inlineStr"/>
+      <c r="AC141" t="inlineStr"/>
+      <c r="AD141" t="inlineStr"/>
+      <c r="AE141" t="inlineStr"/>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AH141" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
+      <c r="W142" t="inlineStr"/>
+      <c r="X142" t="inlineStr"/>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr"/>
+      <c r="AD142" t="inlineStr"/>
+      <c r="AE142" t="inlineStr"/>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AH142" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
+      <c r="W143" t="inlineStr"/>
+      <c r="X143" t="inlineStr"/>
+      <c r="Y143" t="inlineStr"/>
+      <c r="Z143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="inlineStr"/>
+      <c r="AD143" t="inlineStr"/>
+      <c r="AE143" t="inlineStr"/>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AH143" t="n">
+        <v>67</v>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
+      <c r="W144" t="inlineStr"/>
+      <c r="X144" t="inlineStr"/>
+      <c r="Y144" t="inlineStr"/>
+      <c r="Z144" t="inlineStr"/>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr"/>
+      <c r="AD144" t="inlineStr"/>
+      <c r="AE144" t="inlineStr"/>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AH144" t="n">
+        <v>69</v>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
+      <c r="W145" t="inlineStr"/>
+      <c r="X145" t="inlineStr"/>
+      <c r="Y145" t="inlineStr"/>
+      <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr"/>
+      <c r="AE145" t="inlineStr"/>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AH145" t="n">
+        <v>78</v>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
+      <c r="W146" t="inlineStr"/>
+      <c r="X146" t="inlineStr"/>
+      <c r="Y146" t="inlineStr"/>
+      <c r="Z146" t="inlineStr"/>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr"/>
+      <c r="AC146" t="inlineStr"/>
+      <c r="AD146" t="inlineStr"/>
+      <c r="AE146" t="inlineStr"/>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AH146" t="n">
+        <v>89</v>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
+      <c r="W147" t="inlineStr"/>
+      <c r="X147" t="inlineStr"/>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr"/>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="inlineStr"/>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="inlineStr"/>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AH147" t="n">
+        <v>96</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
         </is>
       </c>
     </row>
@@ -6631,7 +8775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE17"/>
+  <dimension ref="A1:AJ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6651,14 +8795,14 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total: 13 horarios</t>
+          <t>Total: 18 horarios</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LÍNEA 141 - LP1912-215 - 07/01/2026</t>
+          <t>LÍNEA 141 - LP1912-215</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -6788,34 +8932,59 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 26</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 27</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 28</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 29</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 30</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>Parada</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 08:29:46</t>
+          <t>Fecha: 07/01/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -6848,11 +9017,16 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ejecuciones: 11 filas</t>
+          <t>Total: 13 horarios</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -6885,6 +9059,11 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6994,39 +9173,64 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Unnamed: 21</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Unnamed: 22</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Unnamed: 23</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Unnamed: 24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Unnamed: 25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Última actualización: 07:37:20</t>
+          <t>Última actualización: 08:29:46</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -7059,9 +9263,18 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ejecuciones: 11 filas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -7082,78 +9295,151 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>07:58:05</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="Y9" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - LP1912-215 - 07/01/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>07:58:05</t>
+          <t>Hora_Scrap</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>Hora_Llegada</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="Y10" t="n">
-        <v>64</v>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>LP1912</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr"/>
@@ -7161,9 +9447,18 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Última actualización: 07:37:20</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -7189,29 +9484,16 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="AD11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -7235,34 +9517,39 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>215C_EL PATO</t>
-        </is>
-      </c>
-      <c r="AD12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -7286,34 +9573,39 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>08:27:16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>215C_EL PATO</t>
-        </is>
-      </c>
-      <c r="AD13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -7344,27 +9636,32 @@
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>08:29:35</t>
+          <t>08:21:45</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -7395,12 +9692,12 @@
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>08:29:35</t>
+          <t>08:21:45</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7409,13 +9706,18 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -7446,27 +9748,32 @@
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>08:31:01</t>
+          <t>08:27:16</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
       </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -7497,25 +9804,310 @@
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
+        <v>73</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
           <t>08:31:01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD19" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>09:42</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>215C_EL PATO</t>
         </is>
       </c>
-      <c r="AD17" t="n">
+      <c r="AD20" t="n">
         <v>71</v>
       </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>LP1912</t>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>67</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
         </is>
       </c>
     </row>
@@ -7530,7 +10122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE23"/>
+  <dimension ref="A1:AJ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7550,14 +10142,14 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total: 19 horarios</t>
+          <t>Total: 25 horarios</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LÍNEA 141 - 6203-6173 - 07/01/2026</t>
+          <t>LÍNEA 141 - 6203-6173</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -7687,34 +10279,59 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 26</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 27</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 28</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 29</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 30</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>Parada</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Última actualización: 08:29:46</t>
+          <t>Fecha: 07/01/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -7747,11 +10364,16 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ejecuciones: 16 filas</t>
+          <t>Total: 19 horarios</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -7784,6 +10406,11 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7893,39 +10520,64 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Unnamed: 21</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Unnamed: 22</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Unnamed: 23</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Unnamed: 24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Unnamed: 25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Última actualización: 07:37:20</t>
+          <t>Última actualización: 08:29:46</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -7958,9 +10610,18 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ejecuciones: 16 filas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -7981,78 +10642,151 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>07:58:11</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>08:19</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>215C_LA PLATA</t>
-        </is>
-      </c>
-      <c r="Y9" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>L6203</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - 6203-6173 - 07/01/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>07:58:16</t>
+          <t>Hora_Scrap</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>Hora_Llegada</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
-        </is>
-      </c>
-      <c r="Y10" t="n">
-        <v>48</v>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr"/>
@@ -8060,9 +10794,18 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Última actualización: 07:37:20</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -8083,34 +10826,21 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>07:58:11</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>215D_LA PLATA</t>
-        </is>
-      </c>
-      <c r="Y11" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>L6203</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -8134,34 +10864,39 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>08:21:51</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>08:26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>07:58:11</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>215C_LA PLATA</t>
         </is>
       </c>
-      <c r="AD12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE12" t="inlineStr">
+      <c r="Y12" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -8185,34 +10920,39 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>08:21:56</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>07:58:16</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>215A_LA PLATA</t>
         </is>
       </c>
-      <c r="AD13" t="n">
-        <v>31</v>
-      </c>
-      <c r="AE13" t="inlineStr">
+      <c r="Y13" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -8236,34 +10976,39 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>08:21:51</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>07:58:11</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>215D_LA PLATA</t>
         </is>
       </c>
-      <c r="AD14" t="n">
-        <v>47</v>
-      </c>
-      <c r="AE14" t="inlineStr">
+      <c r="Y14" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -8294,27 +11039,32 @@
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>08:27:27</t>
+          <t>08:21:51</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>L6173</t>
-        </is>
-      </c>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -8345,27 +11095,32 @@
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>08:27:22</t>
+          <t>08:21:56</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>215D_LA PLATA</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>L6203</t>
-        </is>
-      </c>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -8396,27 +11151,32 @@
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>08:27:27</t>
+          <t>08:21:51</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>215B_LP-P MOR-40 Y 115</t>
+          <t>215D_LA PLATA</t>
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>L6173</t>
-        </is>
-      </c>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -8447,12 +11207,12 @@
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>08:29:46</t>
+          <t>08:27:27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8461,13 +11221,18 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
       </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -8498,12 +11263,12 @@
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>08:29:40</t>
+          <t>08:27:22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -8512,13 +11277,18 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>
       </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -8549,12 +11319,12 @@
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>08:29:46</t>
+          <t>08:27:27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -8563,13 +11333,18 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
       </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -8600,12 +11375,12 @@
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>08:31:11</t>
+          <t>08:29:46</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -8614,13 +11389,18 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
       </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -8651,12 +11431,12 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>08:31:06</t>
+          <t>08:29:40</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -8665,13 +11445,18 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>
       </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -8702,25 +11487,366 @@
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
+          <t>08:29:46</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>93</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
           <t>08:31:11</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>08:31:06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>215D_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>08:31:11</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
         <is>
           <t>10:03</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>215B_LP-P MOR-40 Y 115</t>
         </is>
       </c>
-      <c r="AD23" t="n">
+      <c r="AD26" t="n">
         <v>92</v>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>L6173</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>08:35:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>215D_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>08:35:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>88</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>08:35:28</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ147"/>
+  <dimension ref="A1:AO170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total: 143 horarios</t>
+          <t>Total: 166 horarios</t>
         </is>
       </c>
     </row>
@@ -610,25 +610,50 @@
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 31</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 32</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 33</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 34</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 35</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="AG4" s="2" t="inlineStr">
+      <c r="AL4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="AH4" s="2" t="inlineStr">
+      <c r="AM4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="AI4" s="2" t="inlineStr">
+      <c r="AN4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr">
+      <c r="AO4" s="2" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
@@ -675,11 +700,16 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Total: 117 horarios</t>
+          <t>Total: 143 horarios</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -717,11 +747,16 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LÍNEA 141 - LP1912 - 07/01/2026</t>
+          <t>LÍNEA 141 - LP1912</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -851,39 +886,64 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
+          <t>Unnamed: 26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Unnamed: 27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Unnamed: 28</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Unnamed: 29</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Unnamed: 30</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Última actualización: 08:29:46</t>
+          <t>Fecha: 07/01/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -921,11 +981,16 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ejecuciones: 94 filas</t>
+          <t>Total: 117 horarios</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -963,6 +1028,11 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1072,44 +1142,69 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Unnamed: 21</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Unnamed: 22</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Unnamed: 23</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Unnamed: 24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Unnamed: 25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Última actualización: 07:37:20</t>
+          <t>Última actualización: 08:29:46</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1147,9 +1242,18 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ejecuciones: 94 filas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -1170,29 +1274,11 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>07:58:05</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>08:01</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="Y12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -1203,50 +1289,141 @@
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - LP1912 - 07/01/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>07:58:05</t>
+          <t>Hora_Scrap</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>Hora_Llegada</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="Y13" t="n">
-        <v>6</v>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>LP1912</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr"/>
@@ -1259,9 +1436,18 @@
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Última actualización: 07:37:20</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -1282,29 +1468,11 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>07:58:05</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>08:11</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="Y14" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -1315,6 +1483,11 @@
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1345,16 +1518,16 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
@@ -1371,6 +1544,11 @@
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1401,16 +1579,16 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
@@ -1427,6 +1605,11 @@
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1457,16 +1640,16 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1483,6 +1666,11 @@
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1513,16 +1701,16 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -1539,6 +1727,11 @@
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1569,16 +1762,16 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -1595,6 +1788,11 @@
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1625,16 +1823,16 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -1651,6 +1849,11 @@
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1681,16 +1884,16 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -1707,6 +1910,11 @@
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1737,16 +1945,16 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -1763,6 +1971,11 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1793,16 +2006,16 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -1819,6 +2032,11 @@
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1849,16 +2067,16 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -1875,6 +2093,11 @@
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1905,16 +2128,16 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -1931,6 +2154,11 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1961,7 +2189,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -1970,7 +2198,7 @@
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -1987,6 +2215,11 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -2017,16 +2250,16 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -2043,6 +2276,11 @@
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -2073,16 +2311,16 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -2099,6 +2337,11 @@
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -2129,16 +2372,16 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -2155,6 +2398,11 @@
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -2185,16 +2433,16 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -2211,6 +2459,11 @@
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -2241,16 +2494,16 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -2267,6 +2520,11 @@
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -2297,16 +2555,16 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -2323,6 +2581,11 @@
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -2353,16 +2616,16 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -2379,6 +2642,11 @@
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -2409,16 +2677,16 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -2435,6 +2703,11 @@
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -2458,39 +2731,44 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="AD35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>73</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -2514,39 +2792,44 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="AD36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -2570,39 +2853,44 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>08:34</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="AD37" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -2638,16 +2926,16 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -2659,6 +2947,11 @@
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -2694,16 +2987,16 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -2715,6 +3008,11 @@
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -2750,16 +3048,16 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -2771,6 +3069,11 @@
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -2806,7 +3109,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -2815,7 +3118,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -2827,6 +3130,11 @@
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -2862,16 +3170,16 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -2883,6 +3191,11 @@
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -2918,16 +3231,16 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -2939,6 +3252,11 @@
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -2974,16 +3292,16 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -2995,6 +3313,11 @@
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -3030,16 +3353,16 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -3051,6 +3374,11 @@
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -3086,16 +3414,16 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -3107,6 +3435,11 @@
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -3142,16 +3475,16 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -3163,6 +3496,11 @@
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -3198,16 +3536,16 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -3219,6 +3557,11 @@
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -3254,16 +3597,16 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -3275,6 +3618,11 @@
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -3310,16 +3658,16 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -3331,6 +3679,11 @@
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -3366,16 +3719,16 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -3387,6 +3740,11 @@
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -3422,16 +3780,16 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -3443,6 +3801,11 @@
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -3478,16 +3841,16 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -3499,6 +3862,11 @@
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -3534,16 +3902,16 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -3555,6 +3923,11 @@
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -3590,16 +3963,16 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -3611,6 +3984,11 @@
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -3646,16 +4024,16 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -3667,6 +4045,11 @@
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -3697,21 +4080,21 @@
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>08:27:16</t>
+          <t>08:21:45</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -3723,6 +4106,11 @@
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="inlineStr"/>
       <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -3753,21 +4141,21 @@
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>08:27:16</t>
+          <t>08:21:45</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -3779,6 +4167,11 @@
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="inlineStr"/>
       <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -3809,21 +4202,21 @@
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>08:27:16</t>
+          <t>08:21:45</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -3835,6 +4228,11 @@
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -3870,16 +4268,16 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -3891,6 +4289,11 @@
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -3926,16 +4329,16 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -3947,6 +4350,11 @@
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -3982,16 +4390,16 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -4003,6 +4411,11 @@
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -4038,7 +4451,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -4047,7 +4460,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -4059,6 +4472,11 @@
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -4094,16 +4512,16 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -4115,6 +4533,11 @@
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -4150,16 +4573,16 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -4171,6 +4594,11 @@
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="inlineStr"/>
       <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -4206,16 +4634,16 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -4227,6 +4655,11 @@
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="inlineStr"/>
       <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -4262,16 +4695,16 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -4283,6 +4716,11 @@
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="inlineStr"/>
       <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -4318,16 +4756,16 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -4339,6 +4777,11 @@
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="inlineStr"/>
       <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -4374,16 +4817,16 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -4395,6 +4838,11 @@
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="inlineStr"/>
       <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -4430,16 +4878,16 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -4451,6 +4899,11 @@
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="inlineStr"/>
       <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -4486,16 +4939,16 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -4507,6 +4960,11 @@
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="inlineStr"/>
       <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -4542,16 +5000,16 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -4563,6 +5021,11 @@
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="inlineStr"/>
       <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -4598,16 +5061,16 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -4619,6 +5082,11 @@
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="inlineStr"/>
       <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -4654,16 +5122,16 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
@@ -4675,6 +5143,11 @@
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="inlineStr"/>
       <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -4710,16 +5183,16 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
@@ -4731,6 +5204,11 @@
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="inlineStr"/>
       <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -4766,16 +5244,16 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
@@ -4787,6 +5265,11 @@
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="inlineStr"/>
       <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -4822,16 +5305,16 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -4843,6 +5326,11 @@
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="inlineStr"/>
       <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -4878,16 +5366,16 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
@@ -4899,6 +5387,11 @@
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="inlineStr"/>
       <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -4929,21 +5422,21 @@
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>08:29:35</t>
+          <t>08:27:16</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
@@ -4955,6 +5448,11 @@
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="inlineStr"/>
       <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -4985,21 +5483,21 @@
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>08:29:35</t>
+          <t>08:27:16</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
@@ -5011,6 +5509,11 @@
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="inlineStr"/>
       <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
@@ -5041,21 +5544,21 @@
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>08:29:35</t>
+          <t>08:27:16</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -5067,6 +5570,11 @@
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="inlineStr"/>
       <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
@@ -5102,16 +5610,16 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -5123,6 +5631,11 @@
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="inlineStr"/>
       <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
@@ -5158,16 +5671,16 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
@@ -5179,6 +5692,11 @@
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="inlineStr"/>
       <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr"/>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr"/>
+      <c r="AN83" t="inlineStr"/>
+      <c r="AO83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
@@ -5214,7 +5732,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -5223,7 +5741,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
@@ -5235,6 +5753,11 @@
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="inlineStr"/>
       <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr"/>
+      <c r="AO84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
@@ -5270,16 +5793,16 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
@@ -5291,6 +5814,11 @@
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="inlineStr"/>
       <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="inlineStr"/>
+      <c r="AL85" t="inlineStr"/>
+      <c r="AM85" t="inlineStr"/>
+      <c r="AN85" t="inlineStr"/>
+      <c r="AO85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
@@ -5326,16 +5854,16 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
@@ -5347,6 +5875,11 @@
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="inlineStr"/>
       <c r="AJ86" t="inlineStr"/>
+      <c r="AK86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="inlineStr"/>
+      <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
@@ -5382,16 +5915,16 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
@@ -5403,6 +5936,11 @@
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="inlineStr"/>
       <c r="AJ87" t="inlineStr"/>
+      <c r="AK87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr"/>
+      <c r="AN87" t="inlineStr"/>
+      <c r="AO87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
@@ -5438,16 +5976,16 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
@@ -5459,6 +5997,11 @@
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="inlineStr"/>
       <c r="AJ88" t="inlineStr"/>
+      <c r="AK88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="inlineStr"/>
+      <c r="AN88" t="inlineStr"/>
+      <c r="AO88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
@@ -5494,16 +6037,16 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
@@ -5515,6 +6058,11 @@
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="inlineStr"/>
       <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr"/>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="inlineStr"/>
+      <c r="AN89" t="inlineStr"/>
+      <c r="AO89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
@@ -5550,16 +6098,16 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
@@ -5571,6 +6119,11 @@
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="inlineStr"/>
       <c r="AJ90" t="inlineStr"/>
+      <c r="AK90" t="inlineStr"/>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="inlineStr"/>
+      <c r="AN90" t="inlineStr"/>
+      <c r="AO90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
@@ -5606,16 +6159,16 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
@@ -5627,6 +6180,11 @@
       <c r="AH91" t="inlineStr"/>
       <c r="AI91" t="inlineStr"/>
       <c r="AJ91" t="inlineStr"/>
+      <c r="AK91" t="inlineStr"/>
+      <c r="AL91" t="inlineStr"/>
+      <c r="AM91" t="inlineStr"/>
+      <c r="AN91" t="inlineStr"/>
+      <c r="AO91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
@@ -5662,16 +6220,16 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="AE92" t="inlineStr">
         <is>
@@ -5683,6 +6241,11 @@
       <c r="AH92" t="inlineStr"/>
       <c r="AI92" t="inlineStr"/>
       <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="inlineStr"/>
+      <c r="AL92" t="inlineStr"/>
+      <c r="AM92" t="inlineStr"/>
+      <c r="AN92" t="inlineStr"/>
+      <c r="AO92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
@@ -5718,16 +6281,16 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -5739,6 +6302,11 @@
       <c r="AH93" t="inlineStr"/>
       <c r="AI93" t="inlineStr"/>
       <c r="AJ93" t="inlineStr"/>
+      <c r="AK93" t="inlineStr"/>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="inlineStr"/>
+      <c r="AN93" t="inlineStr"/>
+      <c r="AO93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
@@ -5774,16 +6342,16 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="AE94" t="inlineStr">
         <is>
@@ -5795,6 +6363,11 @@
       <c r="AH94" t="inlineStr"/>
       <c r="AI94" t="inlineStr"/>
       <c r="AJ94" t="inlineStr"/>
+      <c r="AK94" t="inlineStr"/>
+      <c r="AL94" t="inlineStr"/>
+      <c r="AM94" t="inlineStr"/>
+      <c r="AN94" t="inlineStr"/>
+      <c r="AO94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
@@ -5830,16 +6403,16 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
@@ -5851,6 +6424,11 @@
       <c r="AH95" t="inlineStr"/>
       <c r="AI95" t="inlineStr"/>
       <c r="AJ95" t="inlineStr"/>
+      <c r="AK95" t="inlineStr"/>
+      <c r="AL95" t="inlineStr"/>
+      <c r="AM95" t="inlineStr"/>
+      <c r="AN95" t="inlineStr"/>
+      <c r="AO95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
@@ -5886,16 +6464,16 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
@@ -5907,6 +6485,11 @@
       <c r="AH96" t="inlineStr"/>
       <c r="AI96" t="inlineStr"/>
       <c r="AJ96" t="inlineStr"/>
+      <c r="AK96" t="inlineStr"/>
+      <c r="AL96" t="inlineStr"/>
+      <c r="AM96" t="inlineStr"/>
+      <c r="AN96" t="inlineStr"/>
+      <c r="AO96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
@@ -5942,16 +6525,16 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
@@ -5963,6 +6546,11 @@
       <c r="AH97" t="inlineStr"/>
       <c r="AI97" t="inlineStr"/>
       <c r="AJ97" t="inlineStr"/>
+      <c r="AK97" t="inlineStr"/>
+      <c r="AL97" t="inlineStr"/>
+      <c r="AM97" t="inlineStr"/>
+      <c r="AN97" t="inlineStr"/>
+      <c r="AO97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
@@ -5998,16 +6586,16 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
@@ -6019,6 +6607,11 @@
       <c r="AH98" t="inlineStr"/>
       <c r="AI98" t="inlineStr"/>
       <c r="AJ98" t="inlineStr"/>
+      <c r="AK98" t="inlineStr"/>
+      <c r="AL98" t="inlineStr"/>
+      <c r="AM98" t="inlineStr"/>
+      <c r="AN98" t="inlineStr"/>
+      <c r="AO98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
@@ -6054,16 +6647,16 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="AE99" t="inlineStr">
         <is>
@@ -6075,6 +6668,11 @@
       <c r="AH99" t="inlineStr"/>
       <c r="AI99" t="inlineStr"/>
       <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr"/>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="inlineStr"/>
+      <c r="AN99" t="inlineStr"/>
+      <c r="AO99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
@@ -6110,16 +6708,16 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="AE100" t="inlineStr">
         <is>
@@ -6131,6 +6729,11 @@
       <c r="AH100" t="inlineStr"/>
       <c r="AI100" t="inlineStr"/>
       <c r="AJ100" t="inlineStr"/>
+      <c r="AK100" t="inlineStr"/>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="inlineStr"/>
+      <c r="AN100" t="inlineStr"/>
+      <c r="AO100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
@@ -6166,16 +6769,16 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AE101" t="inlineStr">
         <is>
@@ -6187,6 +6790,11 @@
       <c r="AH101" t="inlineStr"/>
       <c r="AI101" t="inlineStr"/>
       <c r="AJ101" t="inlineStr"/>
+      <c r="AK101" t="inlineStr"/>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="inlineStr"/>
+      <c r="AN101" t="inlineStr"/>
+      <c r="AO101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
@@ -6217,21 +6825,21 @@
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>08:31:01</t>
+          <t>08:29:35</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
@@ -6243,6 +6851,11 @@
       <c r="AH102" t="inlineStr"/>
       <c r="AI102" t="inlineStr"/>
       <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="inlineStr"/>
+      <c r="AN102" t="inlineStr"/>
+      <c r="AO102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
@@ -6273,21 +6886,21 @@
       <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>08:31:01</t>
+          <t>08:29:35</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
@@ -6299,6 +6912,11 @@
       <c r="AH103" t="inlineStr"/>
       <c r="AI103" t="inlineStr"/>
       <c r="AJ103" t="inlineStr"/>
+      <c r="AK103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="inlineStr"/>
+      <c r="AN103" t="inlineStr"/>
+      <c r="AO103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
@@ -6329,21 +6947,21 @@
       <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>08:31:01</t>
+          <t>08:29:35</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="AE104" t="inlineStr">
         <is>
@@ -6355,6 +6973,11 @@
       <c r="AH104" t="inlineStr"/>
       <c r="AI104" t="inlineStr"/>
       <c r="AJ104" t="inlineStr"/>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="inlineStr"/>
+      <c r="AN104" t="inlineStr"/>
+      <c r="AO104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
@@ -6390,16 +7013,16 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AE105" t="inlineStr">
         <is>
@@ -6411,6 +7034,11 @@
       <c r="AH105" t="inlineStr"/>
       <c r="AI105" t="inlineStr"/>
       <c r="AJ105" t="inlineStr"/>
+      <c r="AK105" t="inlineStr"/>
+      <c r="AL105" t="inlineStr"/>
+      <c r="AM105" t="inlineStr"/>
+      <c r="AN105" t="inlineStr"/>
+      <c r="AO105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
@@ -6446,16 +7074,16 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE106" t="inlineStr">
         <is>
@@ -6467,6 +7095,11 @@
       <c r="AH106" t="inlineStr"/>
       <c r="AI106" t="inlineStr"/>
       <c r="AJ106" t="inlineStr"/>
+      <c r="AK106" t="inlineStr"/>
+      <c r="AL106" t="inlineStr"/>
+      <c r="AM106" t="inlineStr"/>
+      <c r="AN106" t="inlineStr"/>
+      <c r="AO106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
@@ -6502,7 +7135,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -6511,7 +7144,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
@@ -6523,6 +7156,11 @@
       <c r="AH107" t="inlineStr"/>
       <c r="AI107" t="inlineStr"/>
       <c r="AJ107" t="inlineStr"/>
+      <c r="AK107" t="inlineStr"/>
+      <c r="AL107" t="inlineStr"/>
+      <c r="AM107" t="inlineStr"/>
+      <c r="AN107" t="inlineStr"/>
+      <c r="AO107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
@@ -6558,16 +7196,16 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AE108" t="inlineStr">
         <is>
@@ -6579,6 +7217,11 @@
       <c r="AH108" t="inlineStr"/>
       <c r="AI108" t="inlineStr"/>
       <c r="AJ108" t="inlineStr"/>
+      <c r="AK108" t="inlineStr"/>
+      <c r="AL108" t="inlineStr"/>
+      <c r="AM108" t="inlineStr"/>
+      <c r="AN108" t="inlineStr"/>
+      <c r="AO108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
@@ -6614,16 +7257,16 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AE109" t="inlineStr">
         <is>
@@ -6635,6 +7278,11 @@
       <c r="AH109" t="inlineStr"/>
       <c r="AI109" t="inlineStr"/>
       <c r="AJ109" t="inlineStr"/>
+      <c r="AK109" t="inlineStr"/>
+      <c r="AL109" t="inlineStr"/>
+      <c r="AM109" t="inlineStr"/>
+      <c r="AN109" t="inlineStr"/>
+      <c r="AO109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
@@ -6670,16 +7318,16 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
@@ -6691,6 +7339,11 @@
       <c r="AH110" t="inlineStr"/>
       <c r="AI110" t="inlineStr"/>
       <c r="AJ110" t="inlineStr"/>
+      <c r="AK110" t="inlineStr"/>
+      <c r="AL110" t="inlineStr"/>
+      <c r="AM110" t="inlineStr"/>
+      <c r="AN110" t="inlineStr"/>
+      <c r="AO110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
@@ -6726,16 +7379,16 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="AE111" t="inlineStr">
         <is>
@@ -6747,6 +7400,11 @@
       <c r="AH111" t="inlineStr"/>
       <c r="AI111" t="inlineStr"/>
       <c r="AJ111" t="inlineStr"/>
+      <c r="AK111" t="inlineStr"/>
+      <c r="AL111" t="inlineStr"/>
+      <c r="AM111" t="inlineStr"/>
+      <c r="AN111" t="inlineStr"/>
+      <c r="AO111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
@@ -6782,16 +7440,16 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
@@ -6803,6 +7461,11 @@
       <c r="AH112" t="inlineStr"/>
       <c r="AI112" t="inlineStr"/>
       <c r="AJ112" t="inlineStr"/>
+      <c r="AK112" t="inlineStr"/>
+      <c r="AL112" t="inlineStr"/>
+      <c r="AM112" t="inlineStr"/>
+      <c r="AN112" t="inlineStr"/>
+      <c r="AO112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
@@ -6838,16 +7501,16 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
@@ -6859,6 +7522,11 @@
       <c r="AH113" t="inlineStr"/>
       <c r="AI113" t="inlineStr"/>
       <c r="AJ113" t="inlineStr"/>
+      <c r="AK113" t="inlineStr"/>
+      <c r="AL113" t="inlineStr"/>
+      <c r="AM113" t="inlineStr"/>
+      <c r="AN113" t="inlineStr"/>
+      <c r="AO113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
@@ -6894,16 +7562,16 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="AE114" t="inlineStr">
         <is>
@@ -6915,6 +7583,11 @@
       <c r="AH114" t="inlineStr"/>
       <c r="AI114" t="inlineStr"/>
       <c r="AJ114" t="inlineStr"/>
+      <c r="AK114" t="inlineStr"/>
+      <c r="AL114" t="inlineStr"/>
+      <c r="AM114" t="inlineStr"/>
+      <c r="AN114" t="inlineStr"/>
+      <c r="AO114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
@@ -6950,16 +7623,16 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AE115" t="inlineStr">
         <is>
@@ -6971,6 +7644,11 @@
       <c r="AH115" t="inlineStr"/>
       <c r="AI115" t="inlineStr"/>
       <c r="AJ115" t="inlineStr"/>
+      <c r="AK115" t="inlineStr"/>
+      <c r="AL115" t="inlineStr"/>
+      <c r="AM115" t="inlineStr"/>
+      <c r="AN115" t="inlineStr"/>
+      <c r="AO115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
@@ -7006,16 +7684,16 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
@@ -7027,6 +7705,11 @@
       <c r="AH116" t="inlineStr"/>
       <c r="AI116" t="inlineStr"/>
       <c r="AJ116" t="inlineStr"/>
+      <c r="AK116" t="inlineStr"/>
+      <c r="AL116" t="inlineStr"/>
+      <c r="AM116" t="inlineStr"/>
+      <c r="AN116" t="inlineStr"/>
+      <c r="AO116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
@@ -7062,16 +7745,16 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
@@ -7083,6 +7766,11 @@
       <c r="AH117" t="inlineStr"/>
       <c r="AI117" t="inlineStr"/>
       <c r="AJ117" t="inlineStr"/>
+      <c r="AK117" t="inlineStr"/>
+      <c r="AL117" t="inlineStr"/>
+      <c r="AM117" t="inlineStr"/>
+      <c r="AN117" t="inlineStr"/>
+      <c r="AO117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
@@ -7118,16 +7806,16 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="AE118" t="inlineStr">
         <is>
@@ -7139,6 +7827,11 @@
       <c r="AH118" t="inlineStr"/>
       <c r="AI118" t="inlineStr"/>
       <c r="AJ118" t="inlineStr"/>
+      <c r="AK118" t="inlineStr"/>
+      <c r="AL118" t="inlineStr"/>
+      <c r="AM118" t="inlineStr"/>
+      <c r="AN118" t="inlineStr"/>
+      <c r="AO118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
@@ -7174,16 +7867,16 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="AE119" t="inlineStr">
         <is>
@@ -7195,6 +7888,11 @@
       <c r="AH119" t="inlineStr"/>
       <c r="AI119" t="inlineStr"/>
       <c r="AJ119" t="inlineStr"/>
+      <c r="AK119" t="inlineStr"/>
+      <c r="AL119" t="inlineStr"/>
+      <c r="AM119" t="inlineStr"/>
+      <c r="AN119" t="inlineStr"/>
+      <c r="AO119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
@@ -7230,16 +7928,16 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AE120" t="inlineStr">
         <is>
@@ -7251,6 +7949,11 @@
       <c r="AH120" t="inlineStr"/>
       <c r="AI120" t="inlineStr"/>
       <c r="AJ120" t="inlineStr"/>
+      <c r="AK120" t="inlineStr"/>
+      <c r="AL120" t="inlineStr"/>
+      <c r="AM120" t="inlineStr"/>
+      <c r="AN120" t="inlineStr"/>
+      <c r="AO120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
@@ -7286,16 +7989,16 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="AE121" t="inlineStr">
         <is>
@@ -7307,6 +8010,11 @@
       <c r="AH121" t="inlineStr"/>
       <c r="AI121" t="inlineStr"/>
       <c r="AJ121" t="inlineStr"/>
+      <c r="AK121" t="inlineStr"/>
+      <c r="AL121" t="inlineStr"/>
+      <c r="AM121" t="inlineStr"/>
+      <c r="AN121" t="inlineStr"/>
+      <c r="AO121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
@@ -7342,16 +8050,16 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="AE122" t="inlineStr">
         <is>
@@ -7363,6 +8071,11 @@
       <c r="AH122" t="inlineStr"/>
       <c r="AI122" t="inlineStr"/>
       <c r="AJ122" t="inlineStr"/>
+      <c r="AK122" t="inlineStr"/>
+      <c r="AL122" t="inlineStr"/>
+      <c r="AM122" t="inlineStr"/>
+      <c r="AN122" t="inlineStr"/>
+      <c r="AO122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
@@ -7398,16 +8111,16 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="AE123" t="inlineStr">
         <is>
@@ -7419,6 +8132,11 @@
       <c r="AH123" t="inlineStr"/>
       <c r="AI123" t="inlineStr"/>
       <c r="AJ123" t="inlineStr"/>
+      <c r="AK123" t="inlineStr"/>
+      <c r="AL123" t="inlineStr"/>
+      <c r="AM123" t="inlineStr"/>
+      <c r="AN123" t="inlineStr"/>
+      <c r="AO123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
@@ -7454,16 +8172,16 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="AE124" t="inlineStr">
         <is>
@@ -7475,6 +8193,11 @@
       <c r="AH124" t="inlineStr"/>
       <c r="AI124" t="inlineStr"/>
       <c r="AJ124" t="inlineStr"/>
+      <c r="AK124" t="inlineStr"/>
+      <c r="AL124" t="inlineStr"/>
+      <c r="AM124" t="inlineStr"/>
+      <c r="AN124" t="inlineStr"/>
+      <c r="AO124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
@@ -7503,34 +8226,39 @@
       <c r="X125" t="inlineStr"/>
       <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="inlineStr"/>
-      <c r="AA125" t="inlineStr"/>
-      <c r="AB125" t="inlineStr"/>
-      <c r="AC125" t="inlineStr"/>
-      <c r="AD125" t="inlineStr"/>
-      <c r="AE125" t="inlineStr"/>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>08:43</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="AH125" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>08:35:18</t>
-        </is>
-      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD125" t="n">
+        <v>73</v>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="inlineStr"/>
+      <c r="AH125" t="inlineStr"/>
+      <c r="AI125" t="inlineStr"/>
+      <c r="AJ125" t="inlineStr"/>
+      <c r="AK125" t="inlineStr"/>
+      <c r="AL125" t="inlineStr"/>
+      <c r="AM125" t="inlineStr"/>
+      <c r="AN125" t="inlineStr"/>
+      <c r="AO125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
@@ -7559,34 +8287,39 @@
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="inlineStr"/>
-      <c r="AA126" t="inlineStr"/>
-      <c r="AB126" t="inlineStr"/>
-      <c r="AC126" t="inlineStr"/>
-      <c r="AD126" t="inlineStr"/>
-      <c r="AE126" t="inlineStr"/>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>08:43</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>81_EL PELIGRO</t>
-        </is>
-      </c>
-      <c r="AH126" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>08:35:18</t>
-        </is>
-      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AD126" t="n">
+        <v>81</v>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="inlineStr"/>
+      <c r="AH126" t="inlineStr"/>
+      <c r="AI126" t="inlineStr"/>
+      <c r="AJ126" t="inlineStr"/>
+      <c r="AK126" t="inlineStr"/>
+      <c r="AL126" t="inlineStr"/>
+      <c r="AM126" t="inlineStr"/>
+      <c r="AN126" t="inlineStr"/>
+      <c r="AO126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
@@ -7615,34 +8348,39 @@
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="inlineStr"/>
-      <c r="AA127" t="inlineStr"/>
-      <c r="AB127" t="inlineStr"/>
-      <c r="AC127" t="inlineStr"/>
-      <c r="AD127" t="inlineStr"/>
-      <c r="AE127" t="inlineStr"/>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>08:44</t>
-        </is>
-      </c>
-      <c r="AG127" t="inlineStr">
-        <is>
-          <t>14_ABASTO</t>
-        </is>
-      </c>
-      <c r="AH127" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>08:35:18</t>
-        </is>
-      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AD127" t="n">
+        <v>93</v>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="inlineStr"/>
+      <c r="AH127" t="inlineStr"/>
+      <c r="AI127" t="inlineStr"/>
+      <c r="AJ127" t="inlineStr"/>
+      <c r="AK127" t="inlineStr"/>
+      <c r="AL127" t="inlineStr"/>
+      <c r="AM127" t="inlineStr"/>
+      <c r="AN127" t="inlineStr"/>
+      <c r="AO127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
@@ -7678,7 +8416,7 @@
       <c r="AE128" t="inlineStr"/>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AG128" t="inlineStr">
@@ -7687,7 +8425,7 @@
         </is>
       </c>
       <c r="AH128" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
@@ -7699,6 +8437,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK128" t="inlineStr"/>
+      <c r="AL128" t="inlineStr"/>
+      <c r="AM128" t="inlineStr"/>
+      <c r="AN128" t="inlineStr"/>
+      <c r="AO128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
@@ -7734,16 +8477,16 @@
       <c r="AE129" t="inlineStr"/>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="AH129" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
@@ -7755,6 +8498,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK129" t="inlineStr"/>
+      <c r="AL129" t="inlineStr"/>
+      <c r="AM129" t="inlineStr"/>
+      <c r="AN129" t="inlineStr"/>
+      <c r="AO129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
@@ -7790,16 +8538,16 @@
       <c r="AE130" t="inlineStr"/>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="AH130" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
@@ -7811,6 +8559,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK130" t="inlineStr"/>
+      <c r="AL130" t="inlineStr"/>
+      <c r="AM130" t="inlineStr"/>
+      <c r="AN130" t="inlineStr"/>
+      <c r="AO130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
@@ -7846,16 +8599,16 @@
       <c r="AE131" t="inlineStr"/>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AH131" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
@@ -7867,6 +8620,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK131" t="inlineStr"/>
+      <c r="AL131" t="inlineStr"/>
+      <c r="AM131" t="inlineStr"/>
+      <c r="AN131" t="inlineStr"/>
+      <c r="AO131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
@@ -7902,16 +8660,16 @@
       <c r="AE132" t="inlineStr"/>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AH132" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
@@ -7923,6 +8681,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK132" t="inlineStr"/>
+      <c r="AL132" t="inlineStr"/>
+      <c r="AM132" t="inlineStr"/>
+      <c r="AN132" t="inlineStr"/>
+      <c r="AO132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
@@ -7958,16 +8721,16 @@
       <c r="AE133" t="inlineStr"/>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="AH133" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
@@ -7979,6 +8742,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK133" t="inlineStr"/>
+      <c r="AL133" t="inlineStr"/>
+      <c r="AM133" t="inlineStr"/>
+      <c r="AN133" t="inlineStr"/>
+      <c r="AO133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
@@ -8014,16 +8782,16 @@
       <c r="AE134" t="inlineStr"/>
       <c r="AF134" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="AH134" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
@@ -8035,6 +8803,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK134" t="inlineStr"/>
+      <c r="AL134" t="inlineStr"/>
+      <c r="AM134" t="inlineStr"/>
+      <c r="AN134" t="inlineStr"/>
+      <c r="AO134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
@@ -8070,16 +8843,16 @@
       <c r="AE135" t="inlineStr"/>
       <c r="AF135" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AH135" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
@@ -8091,6 +8864,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK135" t="inlineStr"/>
+      <c r="AL135" t="inlineStr"/>
+      <c r="AM135" t="inlineStr"/>
+      <c r="AN135" t="inlineStr"/>
+      <c r="AO135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
@@ -8126,16 +8904,16 @@
       <c r="AE136" t="inlineStr"/>
       <c r="AF136" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AH136" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
@@ -8147,6 +8925,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK136" t="inlineStr"/>
+      <c r="AL136" t="inlineStr"/>
+      <c r="AM136" t="inlineStr"/>
+      <c r="AN136" t="inlineStr"/>
+      <c r="AO136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
@@ -8182,16 +8965,16 @@
       <c r="AE137" t="inlineStr"/>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="AH137" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
@@ -8203,6 +8986,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK137" t="inlineStr"/>
+      <c r="AL137" t="inlineStr"/>
+      <c r="AM137" t="inlineStr"/>
+      <c r="AN137" t="inlineStr"/>
+      <c r="AO137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
@@ -8238,16 +9026,16 @@
       <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="AH138" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
@@ -8259,6 +9047,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK138" t="inlineStr"/>
+      <c r="AL138" t="inlineStr"/>
+      <c r="AM138" t="inlineStr"/>
+      <c r="AN138" t="inlineStr"/>
+      <c r="AO138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
@@ -8294,16 +9087,16 @@
       <c r="AE139" t="inlineStr"/>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="AH139" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
@@ -8315,6 +9108,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK139" t="inlineStr"/>
+      <c r="AL139" t="inlineStr"/>
+      <c r="AM139" t="inlineStr"/>
+      <c r="AN139" t="inlineStr"/>
+      <c r="AO139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
@@ -8350,16 +9148,16 @@
       <c r="AE140" t="inlineStr"/>
       <c r="AF140" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="AH140" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
@@ -8371,6 +9169,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK140" t="inlineStr"/>
+      <c r="AL140" t="inlineStr"/>
+      <c r="AM140" t="inlineStr"/>
+      <c r="AN140" t="inlineStr"/>
+      <c r="AO140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
@@ -8406,16 +9209,16 @@
       <c r="AE141" t="inlineStr"/>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AH141" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
@@ -8427,6 +9230,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK141" t="inlineStr"/>
+      <c r="AL141" t="inlineStr"/>
+      <c r="AM141" t="inlineStr"/>
+      <c r="AN141" t="inlineStr"/>
+      <c r="AO141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
@@ -8462,16 +9270,16 @@
       <c r="AE142" t="inlineStr"/>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="AH142" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
@@ -8483,6 +9291,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK142" t="inlineStr"/>
+      <c r="AL142" t="inlineStr"/>
+      <c r="AM142" t="inlineStr"/>
+      <c r="AN142" t="inlineStr"/>
+      <c r="AO142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
@@ -8518,16 +9331,16 @@
       <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="AH143" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
@@ -8539,6 +9352,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK143" t="inlineStr"/>
+      <c r="AL143" t="inlineStr"/>
+      <c r="AM143" t="inlineStr"/>
+      <c r="AN143" t="inlineStr"/>
+      <c r="AO143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
@@ -8574,16 +9392,16 @@
       <c r="AE144" t="inlineStr"/>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="AH144" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
@@ -8595,6 +9413,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK144" t="inlineStr"/>
+      <c r="AL144" t="inlineStr"/>
+      <c r="AM144" t="inlineStr"/>
+      <c r="AN144" t="inlineStr"/>
+      <c r="AO144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
@@ -8630,16 +9453,16 @@
       <c r="AE145" t="inlineStr"/>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="AH145" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
@@ -8651,6 +9474,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK145" t="inlineStr"/>
+      <c r="AL145" t="inlineStr"/>
+      <c r="AM145" t="inlineStr"/>
+      <c r="AN145" t="inlineStr"/>
+      <c r="AO145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
@@ -8686,16 +9514,16 @@
       <c r="AE146" t="inlineStr"/>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="AH146" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
@@ -8707,6 +9535,11 @@
           <t>08:35:18</t>
         </is>
       </c>
+      <c r="AK146" t="inlineStr"/>
+      <c r="AL146" t="inlineStr"/>
+      <c r="AM146" t="inlineStr"/>
+      <c r="AN146" t="inlineStr"/>
+      <c r="AO146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
@@ -8742,25 +9575,1433 @@
       <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="inlineStr">
         <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AH147" t="n">
+        <v>69</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr"/>
+      <c r="AL147" t="inlineStr"/>
+      <c r="AM147" t="inlineStr"/>
+      <c r="AN147" t="inlineStr"/>
+      <c r="AO147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
+      <c r="W148" t="inlineStr"/>
+      <c r="X148" t="inlineStr"/>
+      <c r="Y148" t="inlineStr"/>
+      <c r="Z148" t="inlineStr"/>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
+      <c r="AC148" t="inlineStr"/>
+      <c r="AD148" t="inlineStr"/>
+      <c r="AE148" t="inlineStr"/>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AH148" t="n">
+        <v>78</v>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr"/>
+      <c r="AL148" t="inlineStr"/>
+      <c r="AM148" t="inlineStr"/>
+      <c r="AN148" t="inlineStr"/>
+      <c r="AO148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
+      <c r="W149" t="inlineStr"/>
+      <c r="X149" t="inlineStr"/>
+      <c r="Y149" t="inlineStr"/>
+      <c r="Z149" t="inlineStr"/>
+      <c r="AA149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr"/>
+      <c r="AC149" t="inlineStr"/>
+      <c r="AD149" t="inlineStr"/>
+      <c r="AE149" t="inlineStr"/>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AH149" t="n">
+        <v>89</v>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr"/>
+      <c r="AL149" t="inlineStr"/>
+      <c r="AM149" t="inlineStr"/>
+      <c r="AN149" t="inlineStr"/>
+      <c r="AO149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
+      <c r="W150" t="inlineStr"/>
+      <c r="X150" t="inlineStr"/>
+      <c r="Y150" t="inlineStr"/>
+      <c r="Z150" t="inlineStr"/>
+      <c r="AA150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr"/>
+      <c r="AC150" t="inlineStr"/>
+      <c r="AD150" t="inlineStr"/>
+      <c r="AE150" t="inlineStr"/>
+      <c r="AF150" t="inlineStr">
+        <is>
           <t>10:11</t>
         </is>
       </c>
-      <c r="AG147" t="inlineStr">
+      <c r="AG150" t="inlineStr">
         <is>
           <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
-      <c r="AH147" t="n">
+      <c r="AH150" t="n">
         <v>96</v>
       </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
         <is>
           <t>08:35:18</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr"/>
+      <c r="AL150" t="inlineStr"/>
+      <c r="AM150" t="inlineStr"/>
+      <c r="AN150" t="inlineStr"/>
+      <c r="AO150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
+      <c r="W151" t="inlineStr"/>
+      <c r="X151" t="inlineStr"/>
+      <c r="Y151" t="inlineStr"/>
+      <c r="Z151" t="inlineStr"/>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="inlineStr"/>
+      <c r="AD151" t="inlineStr"/>
+      <c r="AE151" t="inlineStr"/>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="inlineStr"/>
+      <c r="AH151" t="inlineStr"/>
+      <c r="AI151" t="inlineStr"/>
+      <c r="AJ151" t="inlineStr"/>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AL151" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AM151" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN151" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
+      <c r="W152" t="inlineStr"/>
+      <c r="X152" t="inlineStr"/>
+      <c r="Y152" t="inlineStr"/>
+      <c r="Z152" t="inlineStr"/>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr"/>
+      <c r="AD152" t="inlineStr"/>
+      <c r="AE152" t="inlineStr"/>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="inlineStr"/>
+      <c r="AH152" t="inlineStr"/>
+      <c r="AI152" t="inlineStr"/>
+      <c r="AJ152" t="inlineStr"/>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="AM152" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN152" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
+      <c r="W153" t="inlineStr"/>
+      <c r="X153" t="inlineStr"/>
+      <c r="Y153" t="inlineStr"/>
+      <c r="Z153" t="inlineStr"/>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr"/>
+      <c r="AD153" t="inlineStr"/>
+      <c r="AE153" t="inlineStr"/>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="inlineStr"/>
+      <c r="AH153" t="inlineStr"/>
+      <c r="AI153" t="inlineStr"/>
+      <c r="AJ153" t="inlineStr"/>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AL153" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AM153" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN153" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
+      <c r="W154" t="inlineStr"/>
+      <c r="X154" t="inlineStr"/>
+      <c r="Y154" t="inlineStr"/>
+      <c r="Z154" t="inlineStr"/>
+      <c r="AA154" t="inlineStr"/>
+      <c r="AB154" t="inlineStr"/>
+      <c r="AC154" t="inlineStr"/>
+      <c r="AD154" t="inlineStr"/>
+      <c r="AE154" t="inlineStr"/>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="inlineStr"/>
+      <c r="AH154" t="inlineStr"/>
+      <c r="AI154" t="inlineStr"/>
+      <c r="AJ154" t="inlineStr"/>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AL154" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AM154" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN154" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+      <c r="W155" t="inlineStr"/>
+      <c r="X155" t="inlineStr"/>
+      <c r="Y155" t="inlineStr"/>
+      <c r="Z155" t="inlineStr"/>
+      <c r="AA155" t="inlineStr"/>
+      <c r="AB155" t="inlineStr"/>
+      <c r="AC155" t="inlineStr"/>
+      <c r="AD155" t="inlineStr"/>
+      <c r="AE155" t="inlineStr"/>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="inlineStr"/>
+      <c r="AH155" t="inlineStr"/>
+      <c r="AI155" t="inlineStr"/>
+      <c r="AJ155" t="inlineStr"/>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AM155" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN155" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
+      <c r="W156" t="inlineStr"/>
+      <c r="X156" t="inlineStr"/>
+      <c r="Y156" t="inlineStr"/>
+      <c r="Z156" t="inlineStr"/>
+      <c r="AA156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="inlineStr"/>
+      <c r="AD156" t="inlineStr"/>
+      <c r="AE156" t="inlineStr"/>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="inlineStr"/>
+      <c r="AH156" t="inlineStr"/>
+      <c r="AI156" t="inlineStr"/>
+      <c r="AJ156" t="inlineStr"/>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="AM156" t="n">
+        <v>30</v>
+      </c>
+      <c r="AN156" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
+      <c r="W157" t="inlineStr"/>
+      <c r="X157" t="inlineStr"/>
+      <c r="Y157" t="inlineStr"/>
+      <c r="Z157" t="inlineStr"/>
+      <c r="AA157" t="inlineStr"/>
+      <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="inlineStr"/>
+      <c r="AD157" t="inlineStr"/>
+      <c r="AE157" t="inlineStr"/>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="inlineStr"/>
+      <c r="AH157" t="inlineStr"/>
+      <c r="AI157" t="inlineStr"/>
+      <c r="AJ157" t="inlineStr"/>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AM157" t="n">
+        <v>34</v>
+      </c>
+      <c r="AN157" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
+      <c r="W158" t="inlineStr"/>
+      <c r="X158" t="inlineStr"/>
+      <c r="Y158" t="inlineStr"/>
+      <c r="Z158" t="inlineStr"/>
+      <c r="AA158" t="inlineStr"/>
+      <c r="AB158" t="inlineStr"/>
+      <c r="AC158" t="inlineStr"/>
+      <c r="AD158" t="inlineStr"/>
+      <c r="AE158" t="inlineStr"/>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="inlineStr"/>
+      <c r="AH158" t="inlineStr"/>
+      <c r="AI158" t="inlineStr"/>
+      <c r="AJ158" t="inlineStr"/>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AL158" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AM158" t="n">
+        <v>37</v>
+      </c>
+      <c r="AN158" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
+      <c r="W159" t="inlineStr"/>
+      <c r="X159" t="inlineStr"/>
+      <c r="Y159" t="inlineStr"/>
+      <c r="Z159" t="inlineStr"/>
+      <c r="AA159" t="inlineStr"/>
+      <c r="AB159" t="inlineStr"/>
+      <c r="AC159" t="inlineStr"/>
+      <c r="AD159" t="inlineStr"/>
+      <c r="AE159" t="inlineStr"/>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="inlineStr"/>
+      <c r="AH159" t="inlineStr"/>
+      <c r="AI159" t="inlineStr"/>
+      <c r="AJ159" t="inlineStr"/>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AM159" t="n">
+        <v>41</v>
+      </c>
+      <c r="AN159" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
+      <c r="W160" t="inlineStr"/>
+      <c r="X160" t="inlineStr"/>
+      <c r="Y160" t="inlineStr"/>
+      <c r="Z160" t="inlineStr"/>
+      <c r="AA160" t="inlineStr"/>
+      <c r="AB160" t="inlineStr"/>
+      <c r="AC160" t="inlineStr"/>
+      <c r="AD160" t="inlineStr"/>
+      <c r="AE160" t="inlineStr"/>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="inlineStr"/>
+      <c r="AH160" t="inlineStr"/>
+      <c r="AI160" t="inlineStr"/>
+      <c r="AJ160" t="inlineStr"/>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AL160" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AM160" t="n">
+        <v>45</v>
+      </c>
+      <c r="AN160" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
+      <c r="W161" t="inlineStr"/>
+      <c r="X161" t="inlineStr"/>
+      <c r="Y161" t="inlineStr"/>
+      <c r="Z161" t="inlineStr"/>
+      <c r="AA161" t="inlineStr"/>
+      <c r="AB161" t="inlineStr"/>
+      <c r="AC161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr"/>
+      <c r="AE161" t="inlineStr"/>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="inlineStr"/>
+      <c r="AH161" t="inlineStr"/>
+      <c r="AI161" t="inlineStr"/>
+      <c r="AJ161" t="inlineStr"/>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AL161" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="AM161" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN161" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
+      <c r="W162" t="inlineStr"/>
+      <c r="X162" t="inlineStr"/>
+      <c r="Y162" t="inlineStr"/>
+      <c r="Z162" t="inlineStr"/>
+      <c r="AA162" t="inlineStr"/>
+      <c r="AB162" t="inlineStr"/>
+      <c r="AC162" t="inlineStr"/>
+      <c r="AD162" t="inlineStr"/>
+      <c r="AE162" t="inlineStr"/>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="inlineStr"/>
+      <c r="AH162" t="inlineStr"/>
+      <c r="AI162" t="inlineStr"/>
+      <c r="AJ162" t="inlineStr"/>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AM162" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN162" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
+      <c r="W163" t="inlineStr"/>
+      <c r="X163" t="inlineStr"/>
+      <c r="Y163" t="inlineStr"/>
+      <c r="Z163" t="inlineStr"/>
+      <c r="AA163" t="inlineStr"/>
+      <c r="AB163" t="inlineStr"/>
+      <c r="AC163" t="inlineStr"/>
+      <c r="AD163" t="inlineStr"/>
+      <c r="AE163" t="inlineStr"/>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="inlineStr"/>
+      <c r="AH163" t="inlineStr"/>
+      <c r="AI163" t="inlineStr"/>
+      <c r="AJ163" t="inlineStr"/>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AM163" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN163" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
+      <c r="W164" t="inlineStr"/>
+      <c r="X164" t="inlineStr"/>
+      <c r="Y164" t="inlineStr"/>
+      <c r="Z164" t="inlineStr"/>
+      <c r="AA164" t="inlineStr"/>
+      <c r="AB164" t="inlineStr"/>
+      <c r="AC164" t="inlineStr"/>
+      <c r="AD164" t="inlineStr"/>
+      <c r="AE164" t="inlineStr"/>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="inlineStr"/>
+      <c r="AH164" t="inlineStr"/>
+      <c r="AI164" t="inlineStr"/>
+      <c r="AJ164" t="inlineStr"/>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AM164" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN164" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
+      <c r="W165" t="inlineStr"/>
+      <c r="X165" t="inlineStr"/>
+      <c r="Y165" t="inlineStr"/>
+      <c r="Z165" t="inlineStr"/>
+      <c r="AA165" t="inlineStr"/>
+      <c r="AB165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr"/>
+      <c r="AD165" t="inlineStr"/>
+      <c r="AE165" t="inlineStr"/>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="inlineStr"/>
+      <c r="AH165" t="inlineStr"/>
+      <c r="AI165" t="inlineStr"/>
+      <c r="AJ165" t="inlineStr"/>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AL165" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="AM165" t="n">
+        <v>57</v>
+      </c>
+      <c r="AN165" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr"/>
+      <c r="W166" t="inlineStr"/>
+      <c r="X166" t="inlineStr"/>
+      <c r="Y166" t="inlineStr"/>
+      <c r="Z166" t="inlineStr"/>
+      <c r="AA166" t="inlineStr"/>
+      <c r="AB166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr"/>
+      <c r="AD166" t="inlineStr"/>
+      <c r="AE166" t="inlineStr"/>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="inlineStr"/>
+      <c r="AH166" t="inlineStr"/>
+      <c r="AI166" t="inlineStr"/>
+      <c r="AJ166" t="inlineStr"/>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AL166" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="AM166" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN166" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr"/>
+      <c r="W167" t="inlineStr"/>
+      <c r="X167" t="inlineStr"/>
+      <c r="Y167" t="inlineStr"/>
+      <c r="Z167" t="inlineStr"/>
+      <c r="AA167" t="inlineStr"/>
+      <c r="AB167" t="inlineStr"/>
+      <c r="AC167" t="inlineStr"/>
+      <c r="AD167" t="inlineStr"/>
+      <c r="AE167" t="inlineStr"/>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="inlineStr"/>
+      <c r="AH167" t="inlineStr"/>
+      <c r="AI167" t="inlineStr"/>
+      <c r="AJ167" t="inlineStr"/>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AL167" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="AM167" t="n">
+        <v>77</v>
+      </c>
+      <c r="AN167" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
+      <c r="W168" t="inlineStr"/>
+      <c r="X168" t="inlineStr"/>
+      <c r="Y168" t="inlineStr"/>
+      <c r="Z168" t="inlineStr"/>
+      <c r="AA168" t="inlineStr"/>
+      <c r="AB168" t="inlineStr"/>
+      <c r="AC168" t="inlineStr"/>
+      <c r="AD168" t="inlineStr"/>
+      <c r="AE168" t="inlineStr"/>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="inlineStr"/>
+      <c r="AH168" t="inlineStr"/>
+      <c r="AI168" t="inlineStr"/>
+      <c r="AJ168" t="inlineStr"/>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AL168" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AM168" t="n">
+        <v>82</v>
+      </c>
+      <c r="AN168" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="inlineStr"/>
+      <c r="Z169" t="inlineStr"/>
+      <c r="AA169" t="inlineStr"/>
+      <c r="AB169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
+      <c r="AE169" t="inlineStr"/>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="inlineStr"/>
+      <c r="AH169" t="inlineStr"/>
+      <c r="AI169" t="inlineStr"/>
+      <c r="AJ169" t="inlineStr"/>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="AM169" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN169" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
+      <c r="W170" t="inlineStr"/>
+      <c r="X170" t="inlineStr"/>
+      <c r="Y170" t="inlineStr"/>
+      <c r="Z170" t="inlineStr"/>
+      <c r="AA170" t="inlineStr"/>
+      <c r="AB170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr"/>
+      <c r="AE170" t="inlineStr"/>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="inlineStr"/>
+      <c r="AH170" t="inlineStr"/>
+      <c r="AI170" t="inlineStr"/>
+      <c r="AJ170" t="inlineStr"/>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AL170" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="AM170" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN170" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
         </is>
       </c>
     </row>
@@ -8775,7 +11016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ22"/>
+  <dimension ref="A1:AO27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8795,7 +11036,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total: 18 horarios</t>
+          <t>Total: 23 horarios</t>
         </is>
       </c>
     </row>
@@ -8957,25 +11198,50 @@
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 31</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 32</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 33</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 34</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 35</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="AG4" s="2" t="inlineStr">
+      <c r="AL4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="AH4" s="2" t="inlineStr">
+      <c r="AM4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="AI4" s="2" t="inlineStr">
+      <c r="AN4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr">
+      <c r="AO4" s="2" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
@@ -9022,11 +11288,16 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Total: 13 horarios</t>
+          <t>Total: 18 horarios</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -9064,11 +11335,16 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LÍNEA 141 - LP1912-215 - 07/01/2026</t>
+          <t>LÍNEA 141 - LP1912-215</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9198,39 +11474,64 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
+          <t>Unnamed: 26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Unnamed: 27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Unnamed: 28</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Unnamed: 29</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Unnamed: 30</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Última actualización: 08:29:46</t>
+          <t>Fecha: 07/01/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -9268,11 +11569,16 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ejecuciones: 11 filas</t>
+          <t>Total: 13 horarios</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -9310,6 +11616,11 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9419,44 +11730,69 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Unnamed: 21</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Unnamed: 22</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Unnamed: 23</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Unnamed: 24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Unnamed: 25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Última actualización: 07:37:20</t>
+          <t>Última actualización: 08:29:46</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -9494,9 +11830,18 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ejecuciones: 11 filas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -9517,29 +11862,11 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>07:58:05</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="Y12" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -9550,50 +11877,141 @@
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - LP1912-215 - 07/01/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>07:58:05</t>
+          <t>Hora_Scrap</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>Hora_Llegada</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="Y13" t="n">
-        <v>64</v>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>LP1912</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr"/>
@@ -9606,9 +12024,18 @@
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Última actualización: 07:37:20</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -9634,34 +12061,21 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="AD14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -9685,39 +12099,44 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>08:21:45</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>215C_EL PATO</t>
-        </is>
-      </c>
-      <c r="AD15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -9741,39 +12160,44 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>08:27:16</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>215C_EL PATO</t>
-        </is>
-      </c>
-      <c r="AD16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>07:58:05</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -9804,21 +12228,21 @@
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>08:29:35</t>
+          <t>08:21:45</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -9830,6 +12254,11 @@
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -9860,12 +12289,12 @@
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>08:29:35</t>
+          <t>08:21:45</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -9874,7 +12303,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -9886,6 +12315,11 @@
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -9916,21 +12350,21 @@
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>08:31:01</t>
+          <t>08:27:16</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -9942,6 +12376,11 @@
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -9972,21 +12411,21 @@
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>08:31:01</t>
+          <t>08:29:35</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -9998,6 +12437,11 @@
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -10026,34 +12470,39 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="AH21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>08:35:18</t>
-        </is>
-      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>08:29:35</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -10082,32 +12531,342 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>08:31:01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>09:42</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>215C_EL PATO</t>
         </is>
       </c>
-      <c r="AH22" t="n">
+      <c r="AD23" t="n">
+        <v>71</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>08:35:18</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
         <v>67</v>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>08:35:18</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="AM26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="AM27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>08:47:20</t>
         </is>
       </c>
     </row>
@@ -10122,7 +12881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ29"/>
+  <dimension ref="A1:AO35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10142,7 +12901,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total: 25 horarios</t>
+          <t>Total: 31 horarios</t>
         </is>
       </c>
     </row>
@@ -10304,25 +13063,50 @@
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
+          <t>Unnamed: 31</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 32</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 33</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 34</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed: 35</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="AG4" s="2" t="inlineStr">
+      <c r="AL4" s="2" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="AH4" s="2" t="inlineStr">
+      <c r="AM4" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="AI4" s="2" t="inlineStr">
+      <c r="AN4" s="2" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr">
+      <c r="AO4" s="2" t="inlineStr">
         <is>
           <t>Hora_Scrap</t>
         </is>
@@ -10369,11 +13153,16 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Total: 19 horarios</t>
+          <t>Total: 25 horarios</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -10411,11 +13200,16 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LÍNEA 141 - 6203-6173 - 07/01/2026</t>
+          <t>LÍNEA 141 - 6203-6173</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -10545,39 +13339,64 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
+          <t>Unnamed: 26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Unnamed: 27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Unnamed: 28</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Unnamed: 29</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Unnamed: 30</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Última actualización: 08:29:46</t>
+          <t>Fecha: 07/01/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -10615,11 +13434,16 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ejecuciones: 16 filas</t>
+          <t>Total: 19 horarios</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -10657,6 +13481,11 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10766,44 +13595,69 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Unnamed: 21</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Unnamed: 22</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Unnamed: 23</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Unnamed: 24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Unnamed: 25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>Hora_Scrap</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Hora_Llegada</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Línea</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>Parada</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Última actualización: 07:37:20</t>
+          <t>Última actualización: 08:29:46</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -10841,9 +13695,18 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ejecuciones: 16 filas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -10864,29 +13727,11 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>07:58:11</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>08:19</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>215C_LA PLATA</t>
-        </is>
-      </c>
-      <c r="Y12" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>L6203</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -10897,50 +13742,141 @@
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LÍNEA 141 - 6203-6173 - 07/01/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Unnamed: 7</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Unnamed: 8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Unnamed: 15</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>07:58:16</t>
+          <t>Hora_Scrap</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>Hora_Llegada</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
-        </is>
-      </c>
-      <c r="Y13" t="n">
-        <v>48</v>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr"/>
@@ -10953,9 +13889,18 @@
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Última actualización: 07:37:20</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -10976,29 +13921,11 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>07:58:11</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>215D_LA PLATA</t>
-        </is>
-      </c>
-      <c r="Y14" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>L6203</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -11009,6 +13936,11 @@
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -11032,39 +13964,44 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>08:21:51</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>08:26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>07:58:11</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>215C_LA PLATA</t>
         </is>
       </c>
-      <c r="AD15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE15" t="inlineStr">
+      <c r="Y15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -11088,39 +14025,44 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>08:21:56</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>07:58:16</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>215A_LA PLATA</t>
         </is>
       </c>
-      <c r="AD16" t="n">
-        <v>31</v>
-      </c>
-      <c r="AE16" t="inlineStr">
+      <c r="Y16" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -11144,39 +14086,44 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>08:21:51</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>07:58:11</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>215D_LA PLATA</t>
         </is>
       </c>
-      <c r="AD17" t="n">
-        <v>47</v>
-      </c>
-      <c r="AE17" t="inlineStr">
+      <c r="Y17" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -11207,25 +14154,25 @@
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>08:27:27</t>
+          <t>08:21:51</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>L6203</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
@@ -11233,6 +14180,11 @@
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -11263,25 +14215,25 @@
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>08:27:22</t>
+          <t>08:21:56</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>215D_LA PLATA</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>L6203</t>
+          <t>L6173</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -11289,6 +14241,11 @@
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -11319,25 +14276,25 @@
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>08:27:27</t>
+          <t>08:21:51</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>215B_LP-P MOR-40 Y 115</t>
+          <t>215D_LA PLATA</t>
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>L6203</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr"/>
@@ -11345,6 +14302,11 @@
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -11375,12 +14337,12 @@
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>08:29:46</t>
+          <t>08:27:27</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -11389,7 +14351,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -11401,6 +14363,11 @@
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -11431,12 +14398,12 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>08:29:40</t>
+          <t>08:27:22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -11445,7 +14412,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -11457,6 +14424,11 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -11487,12 +14459,12 @@
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>08:29:46</t>
+          <t>08:27:27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11501,7 +14473,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -11513,6 +14485,11 @@
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -11543,12 +14520,12 @@
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>08:31:11</t>
+          <t>08:29:46</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11557,7 +14534,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -11569,6 +14546,11 @@
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -11599,12 +14581,12 @@
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>08:31:06</t>
+          <t>08:29:40</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -11613,7 +14595,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -11625,6 +14607,11 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -11655,12 +14642,12 @@
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>08:31:11</t>
+          <t>08:29:46</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -11669,7 +14656,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -11681,6 +14668,11 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -11709,34 +14701,39 @@
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>08:31:11</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
         <is>
           <t>215A_LA PLATA</t>
         </is>
       </c>
-      <c r="AH27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AD27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE27" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>08:35:28</t>
-        </is>
-      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -11765,34 +14762,39 @@
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>08:31:06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
         <is>
           <t>09:09</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>215D_LA PLATA</t>
         </is>
       </c>
-      <c r="AH28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AD28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE28" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>08:35:23</t>
-        </is>
-      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -11821,32 +14823,403 @@
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>08:31:11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
         <is>
           <t>10:03</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>215B_LP-P MOR-40 Y 115</t>
         </is>
       </c>
-      <c r="AH29" t="n">
+      <c r="AD29" t="n">
+        <v>92</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>08:35:28</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>215D_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>08:35:23</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
         <v>88</v>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AI32" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
       </c>
-      <c r="AJ29" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>08:35:28</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AM33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>08:47:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>215D_LA PLATA</t>
+        </is>
+      </c>
+      <c r="AM34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>08:47:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="AM35" t="n">
+        <v>76</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>08:47:30</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:35:27</t>
+          <t>Última actualización: 13:45:43</t>
         </is>
       </c>
     </row>
@@ -482,17 +482,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>16_P MOR-167 Y 521</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16_P MOR-167 Y 521</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:35:27</t>
+          <t>Última actualización: 13:45:43</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13:35:16</t>
+          <t>13:45:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:35:27</t>
+          <t>Última actualización: 13:45:43</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13:35:27</t>
+          <t>13:45:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13:35:22</t>
+          <t>13:45:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:45:43</t>
+          <t>Última actualización: 14:32:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 12 filas únicas</t>
+          <t>Ejecuciones: 15 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16_P MOR-167 Y 521</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,12 +707,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,23 +757,98 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>14:32:45</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>89</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>14:32:45</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>92</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14:32:45</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>92</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -803,7 +878,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:45:43</t>
+          <t>Última actualización: 14:32:55</t>
         </is>
       </c>
     </row>
@@ -844,7 +919,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13:45:33</t>
+          <t>14:32:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -858,7 +933,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -890,7 +965,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:45:43</t>
+          <t>Última actualización: 14:32:55</t>
         </is>
       </c>
     </row>
@@ -931,50 +1006,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13:45:43</t>
+          <t>14:32:50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215D_LA PLATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>L6203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13:45:38</t>
+          <t>14:32:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215D_LA PLATA</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>L6203</t>
+          <t>L6173</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:32:55</t>
+          <t>Última actualización: 14:57:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 15 filas únicas</t>
+          <t>Ejecuciones: 19 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -846,9 +846,109 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14:57:33</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>71</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>14:57:33</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>83</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>14:57:33</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>84</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>14:57:33</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>86</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -878,7 +978,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:32:55</t>
+          <t>Última actualización: 14:57:43</t>
         </is>
       </c>
     </row>
@@ -919,21 +1019,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14:32:45</t>
+          <t>14:57:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -965,7 +1065,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:32:55</t>
+          <t>Última actualización: 14:57:43</t>
         </is>
       </c>
     </row>
@@ -1006,50 +1106,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14:32:50</t>
+          <t>14:57:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215D_LA PLATA</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>L6203</t>
+          <t>L6173</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14:32:55</t>
+          <t>14:57:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:57:43</t>
+          <t>Última actualización: 15:47:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 19 filas únicas</t>
+          <t>Ejecuciones: 22 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,12 +557,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>17_179 Y 38</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,21 +882,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -932,23 +932,98 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D24" t="n">
+        <v>77</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>15:47:41</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>86</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>15:47:41</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>94</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>15:47:41</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>97</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -965,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -978,14 +1053,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:57:43</t>
+          <t>Última actualización: 15:47:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
+          <t>Ejecuciones: 2 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1094,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>15:47:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1033,9 +1108,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>15:47:41</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>77</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1052,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1065,14 +1165,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:57:43</t>
+          <t>Última actualización: 15:47:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas únicas</t>
+          <t>Ejecuciones: 3 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1106,50 +1206,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14:57:43</t>
+          <t>15:47:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>L6203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14:57:38</t>
+          <t>15:47:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215C_LA PLATA</t>
+          <t>215B_LP-P MOR-40 Y 115</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>L6203</t>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15:47:52</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>87</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>L6173</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:47:52</t>
+          <t>Última actualización: 16:27:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 22 filas únicas</t>
+          <t>Ejecuciones: 24 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>17_179 Y 38</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,12 +782,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17_179 Y 38</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,21 +882,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -932,21 +932,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -957,21 +957,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1007,23 +1007,73 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>85</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16:27:08</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>86</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16:27:08</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>97</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1040,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,14 +1103,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:47:52</t>
+          <t>Última actualización: 16:27:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1094,48 +1144,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15:47:41</t>
+          <t>16:27:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>15:47:41</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>77</v>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1165,7 +1190,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:47:52</t>
+          <t>Última actualización: 16:27:20</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1231,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15:47:47</t>
+          <t>16:27:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215C_LA PLATA</t>
+          <t>215B_LP-P MOR-40 Y 115</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1224,28 +1249,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>L6203</t>
+          <t>L6173</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15:47:52</t>
+          <t>16:27:19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215B_LP-P MOR-40 Y 115</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1256,25 +1281,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15:47:52</t>
+          <t>16:27:14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:27:20</t>
+          <t>Última actualización: 16:44:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 24 filas únicas</t>
+          <t>Ejecuciones: 22 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,17 +482,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_179 Y 38</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,17 +557,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17_179 Y 38</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,12 +657,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,17 +782,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,21 +882,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_P MOR-167 Y 521</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -907,17 +907,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -932,21 +932,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -957,21 +957,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -982,12 +982,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1007,73 +1007,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16:27:08</t>
+          <t>16:44:44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>16:27:08</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>86</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>16:27:08</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>17_ROMERO</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>97</v>
-      </c>
-      <c r="E29" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1090,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1103,66 +1053,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:27:20</t>
+          <t>Última actualización: 16:44:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Scrap</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>16:27:08</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>38</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
+          <t>Ejecuciones: 0 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1088,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:27:20</t>
+          <t>Última actualización: 16:44:55</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1129,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16:27:19</t>
+          <t>16:44:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1245,7 +1143,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1256,7 +1154,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16:27:19</t>
+          <t>16:44:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1270,7 +1168,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1281,12 +1179,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16:27:14</t>
+          <t>16:44:50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1295,7 +1193,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:44:55</t>
+          <t>Última actualización: 16:58:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 22 filas únicas</t>
+          <t>Ejecuciones: 23 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17_179 Y 38</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>16_P MOR-167 Y 521</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,21 +882,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16_P MOR-167 Y 521</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -932,21 +932,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -957,21 +957,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1007,23 +1007,48 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16:44:44</t>
+          <t>16:58:20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>11X44_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>94</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16:58:20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>97</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1040,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,14 +1078,91 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:44:55</t>
+          <t>Última actualización: 16:58:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 0 filas únicas</t>
+          <t>Ejecuciones: 2 filas únicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>16:58:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>16:58:20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,14 +1190,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:44:55</t>
+          <t>Última actualización: 16:58:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 3 filas únicas</t>
+          <t>Ejecuciones: 2 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1129,21 +1231,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16:44:55</t>
+          <t>16:58:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215B_LP-P MOR-40 Y 115</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1154,48 +1256,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16:44:55</t>
+          <t>16:58:25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t>L6173</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>16:44:50</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>215C_LA PLATA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>79</v>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:58:30</t>
+          <t>Última actualización: 17:36:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 23 filas únicas</t>
+          <t>Ejecuciones: 19 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,12 +482,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_P MOR-167 Y 521</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,12 +657,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16_P MOR-167 Y 521</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>14X44_ABASTO</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,21 +882,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -932,123 +932,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>16:58:20</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>18:25</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>14_ABASTO</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>87</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>16:58:20</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>215C_EL PATO</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>90</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>16:58:20</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>18:32</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>11X44_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>94</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>16:58:20</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>18:35</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>17_ROMERO</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>97</v>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1065,7 +965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1078,14 +978,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:58:30</t>
+          <t>Última actualización: 17:36:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1119,48 +1019,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16:58:20</t>
+          <t>17:36:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>16:58:20</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>215C_EL PATO</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>90</v>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1190,7 +1065,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:58:30</t>
+          <t>Última actualización: 17:36:12</t>
         </is>
       </c>
     </row>
@@ -1231,50 +1106,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16:58:30</t>
+          <t>17:36:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>L6203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16:58:25</t>
+          <t>17:36:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215C_LA PLATA</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>L6203</t>
+          <t>L6173</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:36:12</t>
+          <t>Última actualización: 17:58:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 19 filas únicas</t>
+          <t>Ejecuciones: 18 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16_P MOR-167 Y 521</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>14X44_ABASTO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14X44_ABASTO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,21 +882,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -907,48 +907,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>17:36:02</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>16_P MOR-SANTA ANA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>95</v>
-      </c>
-      <c r="E24" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -978,7 +953,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:36:12</t>
+          <t>Última actualización: 17:58:38</t>
         </is>
       </c>
     </row>
@@ -1019,7 +994,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17:36:02</t>
+          <t>17:58:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1033,7 +1008,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1065,7 +1040,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:36:12</t>
+          <t>Última actualización: 17:58:38</t>
         </is>
       </c>
     </row>
@@ -1106,46 +1081,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17:36:07</t>
+          <t>17:58:38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215C_LA PLATA</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>L6203</t>
+          <t>L6173</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17:36:12</t>
+          <t>17:58:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215B_LP-P MOR-1 Y 57</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:58:38</t>
+          <t>Última actualización: 18:30:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 18 filas únicas</t>
+          <t>Ejecuciones: 17 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,12 +482,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>14X44_ABASTO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14X44_ABASTO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,17 +707,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,48 +882,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>17:58:27</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>19:29</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>91</v>
-      </c>
-      <c r="E23" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -953,7 +928,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:58:38</t>
+          <t>Última actualización: 18:30:41</t>
         </is>
       </c>
     </row>
@@ -994,12 +969,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17:58:27</t>
+          <t>18:30:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1008,7 +983,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1027,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,14 +1015,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:58:38</t>
+          <t>Última actualización: 18:30:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas únicas</t>
+          <t>Ejecuciones: 3 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1056,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17:58:38</t>
+          <t>18:30:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1095,7 +1070,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1106,12 +1081,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17:58:38</t>
+          <t>18:30:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1120,11 +1095,36 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>18:30:36</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>84</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:30:41</t>
+          <t>Última actualización: 18:48:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 17 filas únicas</t>
+          <t>Ejecuciones: 23 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>14X44_ABASTO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,12 +507,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14X44_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -896,9 +896,159 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>18:48:24</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>82</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>18:48:24</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16_P MOR-167 Y 521</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>82</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>18:48:24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>85</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>18:48:24</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>93</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>18:48:24</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>94</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>18:48:24</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>95</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -915,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,14 +1078,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:30:41</t>
+          <t>Última actualización: 18:48:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
+          <t>Ejecuciones: 2 filas únicas</t>
         </is>
       </c>
     </row>
@@ -969,7 +1119,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18:30:30</t>
+          <t>18:48:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -983,9 +1133,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>18:48:24</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>95</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1002,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,14 +1190,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:30:41</t>
+          <t>Última actualización: 18:48:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 3 filas únicas</t>
+          <t>Ejecuciones: 2 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1056,21 +1231,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18:30:41</t>
+          <t>18:48:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215B_LP-P MOR-1 Y 57</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1081,48 +1256,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18:30:41</t>
+          <t>18:48:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215B_LP-P MOR-1 Y 57</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t>L6173</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>18:30:36</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>19:54</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>215C_LA PLATA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>84</v>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:48:35</t>
+          <t>Última actualización: 19:28:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 23 filas únicas</t>
+          <t>Ejecuciones: 17 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14X44_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,12 +507,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,17 +557,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,12 +682,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,173 +882,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>18:48:24</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>82</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>18:48:24</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>16_P MOR-167 Y 521</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>82</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>18:48:24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>85</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>18:48:24</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>20:21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>93</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>18:48:24</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>94</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>18:48:24</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>20:23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>95</v>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1078,7 +928,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:48:35</t>
+          <t>Última actualización: 19:28:41</t>
         </is>
       </c>
     </row>
@@ -1119,7 +969,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1133,7 +983,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1144,7 +994,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18:48:24</t>
+          <t>19:28:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1158,7 +1008,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1190,7 +1040,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:48:35</t>
+          <t>Última actualización: 19:28:41</t>
         </is>
       </c>
     </row>
@@ -1231,50 +1081,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18:48:35</t>
+          <t>19:28:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215B_LP-P MOR-1 Y 57</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>L6203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18:48:30</t>
+          <t>19:28:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215C_LA PLATA</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>L6203</t>
+          <t>L6173</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:28:41</t>
+          <t>Última actualización: 19:49:40</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,12 +507,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,12 +532,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>11X44_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,12 +682,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,21 +882,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:28:41</t>
+          <t>Última actualización: 19:49:40</t>
         </is>
       </c>
     </row>
@@ -969,21 +969,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -994,21 +994,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19:28:30</t>
+          <t>19:49:29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,14 +1040,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:28:41</t>
+          <t>Última actualización: 19:49:40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1081,48 +1081,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19:28:35</t>
+          <t>19:49:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215C_LA PLATA</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>L6203</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>19:28:41</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>20:39</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>215A_LA PLATA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>71</v>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:49:40</t>
+          <t>Última actualización: 20:28:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 17 filas únicas</t>
+          <t>Ejecuciones: 14 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>11X44_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11X44_ETCHEVERRY</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,98 +807,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>19:49:29</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>79</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>19:49:29</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>21:21</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>92</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>19:49:29</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>21:23</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>94</v>
-      </c>
-      <c r="E22" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -928,7 +853,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:49:40</t>
+          <t>Última actualización: 20:28:34</t>
         </is>
       </c>
     </row>
@@ -969,21 +894,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -994,17 +919,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19:49:29</t>
+          <t>20:28:23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1027,7 +952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,14 +965,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:49:40</t>
+          <t>Última actualización: 20:28:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
+          <t>Ejecuciones: 3 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1006,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19:49:40</t>
+          <t>20:28:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1095,9 +1020,59 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20:28:29</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>61</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20:28:34</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>97</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:28:34</t>
+          <t>Última actualización: 20:46:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 14 filas únicas</t>
+          <t>Ejecuciones: 18 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,12 +482,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:32</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,23 +807,123 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:56</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>82</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20:46:23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>17_ROMERO</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>88</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D20" t="n">
+        <v>82</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20:46:23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>87</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20:46:23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>22:19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>93</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20:46:23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>96</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -853,7 +953,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:28:34</t>
+          <t>Última actualización: 20:46:34</t>
         </is>
       </c>
     </row>
@@ -894,7 +994,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -908,7 +1008,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -919,7 +1019,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20:28:23</t>
+          <t>20:46:23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -933,7 +1033,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -965,7 +1065,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:28:34</t>
+          <t>Última actualización: 20:46:34</t>
         </is>
       </c>
     </row>
@@ -1006,71 +1106,71 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20:28:34</t>
+          <t>20:46:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>L6203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20:28:29</t>
+          <t>20:46:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215C_LA PLATA</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>L6203</t>
+          <t>L6173</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20:28:34</t>
+          <t>20:46:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215B_LP-P MOR-40 Y 115</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>

--- a/horarios-141-2026-01-07.xlsx
+++ b/horarios-141-2026-01-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:46:34</t>
+          <t>Última actualización: 23:12:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 18 filas únicas</t>
+          <t>Ejecuciones: 2 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20:46:23</t>
+          <t>23:12:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11X44_ETCHEVERRY</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,423 +507,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20:46:23</t>
+          <t>23:12:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>215_ALUAR</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>20:54</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>21:05</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>19</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>215B_EL PATO</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>22</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>21:13</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>27</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>21:21</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>35</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>21:23</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>37</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>21:32</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>46</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>21:46</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>60</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>21:47</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>61</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>21:49</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>63</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21:53</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>67</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>22:08</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>82</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>22:08</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>17_ROMERO</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>82</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>22:13</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>17_ROMERO</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>87</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>22:19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>93</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>22:22</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>96</v>
-      </c>
-      <c r="E23" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -940,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -953,14 +553,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:46:34</t>
+          <t>Última actualización: 23:12:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
         </is>
       </c>
     </row>
@@ -994,48 +594,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20:46:23</t>
+          <t>23:12:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>215_ALUAR</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>20:46:23</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>21:47</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>61</v>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1052,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1065,116 +640,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:46:34</t>
+          <t>Última actualización: 23:12:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 3 filas únicas</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Scrap</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>20:46:29</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>21:29</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>215C_LA PLATA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>43</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>L6203</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>20:46:34</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>22:05</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>215A_LA PLATA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>79</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>L6173</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>20:46:34</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>22:20</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>215B_LP-P MOR-40 Y 115</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>94</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>L6173</t>
+          <t>Ejecuciones: 0 filas únicas</t>
         </is>
       </c>
     </row>
